--- a/results/results_fase1.xlsx
+++ b/results/results_fase1.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Matteo\UNI\Magistrale AI\tesi\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Matteo\UNI\Magistrale AI\tesi\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EA5826E-32B4-45E1-BD6E-726E559067EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21ADB951-551F-4C9C-9A4D-D9844DEBB94B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{59FC6393-1880-4F9F-B64F-8EC30F610A37}"/>
   </bookViews>
@@ -554,17 +554,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -1034,7 +1032,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A647EDCB-5CAF-479A-87D3-342C45641633}">
-  <dimension ref="A1:AC79"/>
+  <dimension ref="A1:AC200"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.85546875" bestFit="1" customWidth="1"/>
@@ -1065,38 +1063,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-      <c r="P1" s="3" t="s">
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
+      <c r="N1" s="3"/>
+      <c r="P1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="Q1" s="2"/>
-      <c r="R1" s="2"/>
-      <c r="S1" s="2"/>
-      <c r="T1" s="2"/>
-      <c r="U1" s="2"/>
-      <c r="V1" s="2"/>
-      <c r="W1" s="2"/>
-      <c r="X1" s="2"/>
-      <c r="Y1" s="2"/>
-      <c r="Z1" s="2"/>
-      <c r="AA1" s="2"/>
-      <c r="AB1" s="2"/>
-      <c r="AC1" s="2"/>
+      <c r="Q1" s="3"/>
+      <c r="R1" s="3"/>
+      <c r="S1" s="3"/>
+      <c r="T1" s="3"/>
+      <c r="U1" s="3"/>
+      <c r="V1" s="3"/>
+      <c r="W1" s="3"/>
+      <c r="X1" s="3"/>
+      <c r="Y1" s="3"/>
+      <c r="Z1" s="3"/>
+      <c r="AA1" s="3"/>
+      <c r="AB1" s="3"/>
+      <c r="AC1" s="3"/>
     </row>
     <row r="2" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
@@ -1185,19 +1183,19 @@
       </c>
     </row>
     <row r="3" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" s="1" t="s">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3" s="1" t="s">
+      <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" t="s">
         <v>19</v>
       </c>
       <c r="F3">
@@ -1215,25 +1213,25 @@
       <c r="J3">
         <v>1117</v>
       </c>
-      <c r="M3" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="P3" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q3" s="1" t="s">
+      <c r="M3" t="s">
+        <v>115</v>
+      </c>
+      <c r="N3" t="s">
+        <v>115</v>
+      </c>
+      <c r="P3" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q3" t="s">
         <v>16</v>
       </c>
-      <c r="R3" s="1" t="s">
+      <c r="R3" t="s">
         <v>17</v>
       </c>
-      <c r="S3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="T3" s="1" t="s">
+      <c r="S3" t="s">
+        <v>18</v>
+      </c>
+      <c r="T3" t="s">
         <v>19</v>
       </c>
       <c r="U3">
@@ -1251,27 +1249,27 @@
       <c r="Y3">
         <v>1381</v>
       </c>
-      <c r="AB3" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="AC3" s="1" t="s">
+      <c r="AB3" t="s">
+        <v>115</v>
+      </c>
+      <c r="AC3" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="4" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" s="1" t="s">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" s="1" t="s">
+      <c r="D4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" t="s">
         <v>19</v>
       </c>
       <c r="F4">
@@ -1289,25 +1287,25 @@
       <c r="J4">
         <v>111</v>
       </c>
-      <c r="M4" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="P4" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q4" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="R4" s="1" t="s">
+      <c r="M4" t="s">
+        <v>115</v>
+      </c>
+      <c r="N4" t="s">
+        <v>115</v>
+      </c>
+      <c r="P4" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>20</v>
+      </c>
+      <c r="R4" t="s">
         <v>21</v>
       </c>
-      <c r="S4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="T4" s="1" t="s">
+      <c r="S4" t="s">
+        <v>18</v>
+      </c>
+      <c r="T4" t="s">
         <v>19</v>
       </c>
       <c r="U4">
@@ -1325,27 +1323,27 @@
       <c r="Y4">
         <v>1351</v>
       </c>
-      <c r="AB4" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="AC4" s="1" t="s">
+      <c r="AB4" t="s">
+        <v>115</v>
+      </c>
+      <c r="AC4" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="5" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" s="1" t="s">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" t="s">
         <v>116</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" t="s">
         <v>117</v>
       </c>
       <c r="F5">
@@ -1363,25 +1361,25 @@
       <c r="J5">
         <v>1142</v>
       </c>
-      <c r="M5" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="N5" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="P5" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q5" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="R5" s="1" t="s">
+      <c r="M5" t="s">
+        <v>115</v>
+      </c>
+      <c r="N5" t="s">
+        <v>115</v>
+      </c>
+      <c r="P5" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>20</v>
+      </c>
+      <c r="R5" t="s">
         <v>22</v>
       </c>
-      <c r="S5" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="T5" s="1" t="s">
+      <c r="S5" t="s">
+        <v>18</v>
+      </c>
+      <c r="T5" t="s">
         <v>19</v>
       </c>
       <c r="U5">
@@ -1399,27 +1397,27 @@
       <c r="Y5">
         <v>1408</v>
       </c>
-      <c r="AB5" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="AC5" s="1" t="s">
+      <c r="AB5" t="s">
+        <v>115</v>
+      </c>
+      <c r="AC5" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="6" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" s="1" t="s">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" t="s">
         <v>118</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" t="s">
         <v>119</v>
       </c>
       <c r="F6">
@@ -1437,25 +1435,25 @@
       <c r="J6">
         <v>119</v>
       </c>
-      <c r="M6" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="P6" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q6" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="R6" s="1" t="s">
+      <c r="M6" t="s">
+        <v>115</v>
+      </c>
+      <c r="N6" t="s">
+        <v>115</v>
+      </c>
+      <c r="P6" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>20</v>
+      </c>
+      <c r="R6" t="s">
         <v>23</v>
       </c>
-      <c r="S6" s="1" t="s">
+      <c r="S6" t="s">
         <v>116</v>
       </c>
-      <c r="T6" s="1" t="s">
+      <c r="T6" t="s">
         <v>117</v>
       </c>
       <c r="U6">
@@ -1473,27 +1471,27 @@
       <c r="Y6">
         <v>1399</v>
       </c>
-      <c r="AB6" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="AC6" s="1" t="s">
+      <c r="AB6" t="s">
+        <v>115</v>
+      </c>
+      <c r="AC6" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="7" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" s="1" t="s">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" t="s">
         <v>24</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" t="s">
         <v>120</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E7" t="s">
         <v>25</v>
       </c>
       <c r="F7">
@@ -1511,25 +1509,25 @@
       <c r="J7">
         <v>1291</v>
       </c>
-      <c r="M7" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="N7" s="1" t="s">
+      <c r="M7" t="s">
+        <v>115</v>
+      </c>
+      <c r="N7" t="s">
         <v>26</v>
       </c>
-      <c r="P7" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q7" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="R7" s="1" t="s">
+      <c r="P7" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>20</v>
+      </c>
+      <c r="R7" t="s">
         <v>24</v>
       </c>
-      <c r="S7" s="1" t="s">
+      <c r="S7" t="s">
         <v>135</v>
       </c>
-      <c r="T7" s="1" t="s">
+      <c r="T7" t="s">
         <v>112</v>
       </c>
       <c r="U7">
@@ -1547,27 +1545,27 @@
       <c r="Y7">
         <v>1498</v>
       </c>
-      <c r="AB7" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="AC7" s="1" t="s">
+      <c r="AB7" t="s">
+        <v>115</v>
+      </c>
+      <c r="AC7" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="8" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" s="1" t="s">
+      <c r="A8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" t="s">
         <v>27</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" t="s">
         <v>121</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E8" t="s">
         <v>28</v>
       </c>
       <c r="F8">
@@ -1585,25 +1583,25 @@
       <c r="J8">
         <v>1348</v>
       </c>
-      <c r="M8" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="N8" s="1" t="s">
+      <c r="M8" t="s">
+        <v>115</v>
+      </c>
+      <c r="N8" t="s">
         <v>2</v>
       </c>
-      <c r="P8" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q8" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="R8" s="1" t="s">
+      <c r="P8" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>20</v>
+      </c>
+      <c r="R8" t="s">
         <v>27</v>
       </c>
-      <c r="S8" s="1" t="s">
+      <c r="S8" t="s">
         <v>136</v>
       </c>
-      <c r="T8" s="1" t="s">
+      <c r="T8" t="s">
         <v>137</v>
       </c>
       <c r="U8">
@@ -1621,27 +1619,27 @@
       <c r="Y8">
         <v>1414</v>
       </c>
-      <c r="AB8" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="AC8" s="1" t="s">
+      <c r="AB8" t="s">
+        <v>115</v>
+      </c>
+      <c r="AC8" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="9" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" s="1" t="s">
+      <c r="A9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" t="s">
         <v>29</v>
       </c>
-      <c r="D9" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E9" s="1" t="s">
+      <c r="D9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" t="s">
         <v>19</v>
       </c>
       <c r="F9">
@@ -1659,25 +1657,25 @@
       <c r="J9">
         <v>106</v>
       </c>
-      <c r="M9" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="N9" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="P9" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q9" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="R9" s="1" t="s">
+      <c r="M9" t="s">
+        <v>115</v>
+      </c>
+      <c r="N9" t="s">
+        <v>115</v>
+      </c>
+      <c r="P9" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>20</v>
+      </c>
+      <c r="R9" t="s">
         <v>29</v>
       </c>
-      <c r="S9" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="T9" s="1" t="s">
+      <c r="S9" t="s">
+        <v>18</v>
+      </c>
+      <c r="T9" t="s">
         <v>19</v>
       </c>
       <c r="U9">
@@ -1695,27 +1693,27 @@
       <c r="Y9">
         <v>1201</v>
       </c>
-      <c r="AB9" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="AC9" s="1" t="s">
+      <c r="AB9" t="s">
+        <v>115</v>
+      </c>
+      <c r="AC9" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="10" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C10" s="1" t="s">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" t="s">
         <v>30</v>
       </c>
-      <c r="D10" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E10" s="1" t="s">
+      <c r="D10" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" t="s">
         <v>19</v>
       </c>
       <c r="F10">
@@ -1733,25 +1731,25 @@
       <c r="J10">
         <v>97</v>
       </c>
-      <c r="M10" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="N10" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="P10" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q10" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="R10" s="1" t="s">
+      <c r="M10" t="s">
+        <v>115</v>
+      </c>
+      <c r="N10" t="s">
+        <v>115</v>
+      </c>
+      <c r="P10" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>20</v>
+      </c>
+      <c r="R10" t="s">
         <v>30</v>
       </c>
-      <c r="S10" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="T10" s="1" t="s">
+      <c r="S10" t="s">
+        <v>18</v>
+      </c>
+      <c r="T10" t="s">
         <v>19</v>
       </c>
       <c r="U10">
@@ -1769,27 +1767,27 @@
       <c r="Y10">
         <v>1159</v>
       </c>
-      <c r="AB10" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="AC10" s="1" t="s">
+      <c r="AB10" t="s">
+        <v>115</v>
+      </c>
+      <c r="AC10" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C11" s="1" t="s">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" t="s">
         <v>31</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D11" t="s">
         <v>122</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="E11" t="s">
         <v>123</v>
       </c>
       <c r="F11">
@@ -1807,25 +1805,25 @@
       <c r="J11">
         <v>867</v>
       </c>
-      <c r="M11" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="N11" s="1" t="s">
+      <c r="M11" t="s">
+        <v>115</v>
+      </c>
+      <c r="N11" t="s">
         <v>32</v>
       </c>
-      <c r="P11" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q11" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="R11" s="1" t="s">
+      <c r="P11" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>20</v>
+      </c>
+      <c r="R11" t="s">
         <v>31</v>
       </c>
-      <c r="S11" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="T11" s="1" t="s">
+      <c r="S11" t="s">
+        <v>18</v>
+      </c>
+      <c r="T11" t="s">
         <v>19</v>
       </c>
       <c r="U11">
@@ -1843,27 +1841,27 @@
       <c r="Y11">
         <v>1019</v>
       </c>
-      <c r="AB11" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="AC11" s="1" t="s">
+      <c r="AB11" t="s">
+        <v>115</v>
+      </c>
+      <c r="AC11" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C12" s="1" t="s">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" t="s">
         <v>33</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D12" t="s">
         <v>34</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="E12" t="s">
         <v>35</v>
       </c>
       <c r="F12">
@@ -1881,25 +1879,25 @@
       <c r="J12">
         <v>983</v>
       </c>
-      <c r="M12" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="N12" s="1" t="s">
+      <c r="M12" t="s">
+        <v>115</v>
+      </c>
+      <c r="N12" t="s">
         <v>36</v>
       </c>
-      <c r="P12" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q12" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="R12" s="1" t="s">
+      <c r="P12" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>20</v>
+      </c>
+      <c r="R12" t="s">
         <v>33</v>
       </c>
-      <c r="S12" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="T12" s="1" t="s">
+      <c r="S12" t="s">
+        <v>18</v>
+      </c>
+      <c r="T12" t="s">
         <v>19</v>
       </c>
       <c r="U12">
@@ -1917,27 +1915,27 @@
       <c r="Y12">
         <v>1052</v>
       </c>
-      <c r="AB12" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="AC12" s="1" t="s">
+      <c r="AB12" t="s">
+        <v>115</v>
+      </c>
+      <c r="AC12" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C13" s="1" t="s">
+      <c r="A13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" t="s">
         <v>37</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D13" t="s">
         <v>38</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="E13" t="s">
         <v>39</v>
       </c>
       <c r="F13">
@@ -1955,25 +1953,25 @@
       <c r="J13">
         <v>1067</v>
       </c>
-      <c r="M13" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="N13" s="1" t="s">
+      <c r="M13" t="s">
+        <v>115</v>
+      </c>
+      <c r="N13" t="s">
         <v>36</v>
       </c>
-      <c r="P13" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q13" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="R13" s="1" t="s">
+      <c r="P13" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>20</v>
+      </c>
+      <c r="R13" t="s">
         <v>37</v>
       </c>
-      <c r="S13" s="1" t="s">
+      <c r="S13" t="s">
         <v>138</v>
       </c>
-      <c r="T13" s="1" t="s">
+      <c r="T13" t="s">
         <v>139</v>
       </c>
       <c r="U13">
@@ -1991,27 +1989,27 @@
       <c r="Y13">
         <v>1184</v>
       </c>
-      <c r="AB13" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="AC13" s="1" t="s">
+      <c r="AB13" t="s">
+        <v>115</v>
+      </c>
+      <c r="AC13" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="14" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C14" s="1" t="s">
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" t="s">
+        <v>20</v>
+      </c>
+      <c r="C14" t="s">
         <v>40</v>
       </c>
-      <c r="D14" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E14" s="1" t="s">
+      <c r="D14" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" t="s">
         <v>19</v>
       </c>
       <c r="F14">
@@ -2029,25 +2027,25 @@
       <c r="J14">
         <v>1081</v>
       </c>
-      <c r="M14" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="N14" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="P14" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q14" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="R14" s="1" t="s">
+      <c r="M14" t="s">
+        <v>115</v>
+      </c>
+      <c r="N14" t="s">
+        <v>115</v>
+      </c>
+      <c r="P14" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>20</v>
+      </c>
+      <c r="R14" t="s">
         <v>40</v>
       </c>
-      <c r="S14" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="T14" s="1" t="s">
+      <c r="S14" t="s">
+        <v>18</v>
+      </c>
+      <c r="T14" t="s">
         <v>19</v>
       </c>
       <c r="U14">
@@ -2065,27 +2063,27 @@
       <c r="Y14">
         <v>1215</v>
       </c>
-      <c r="AB14" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="AC14" s="1" t="s">
+      <c r="AB14" t="s">
+        <v>115</v>
+      </c>
+      <c r="AC14" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="15" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C15" s="1" t="s">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" t="s">
         <v>41</v>
       </c>
-      <c r="D15" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E15" s="1" t="s">
+      <c r="D15" t="s">
+        <v>18</v>
+      </c>
+      <c r="E15" t="s">
         <v>19</v>
       </c>
       <c r="F15">
@@ -2103,25 +2101,25 @@
       <c r="J15">
         <v>1074</v>
       </c>
-      <c r="M15" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="N15" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="P15" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q15" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="R15" s="1" t="s">
+      <c r="M15" t="s">
+        <v>115</v>
+      </c>
+      <c r="N15" t="s">
+        <v>115</v>
+      </c>
+      <c r="P15" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>20</v>
+      </c>
+      <c r="R15" t="s">
         <v>41</v>
       </c>
-      <c r="S15" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="T15" s="1" t="s">
+      <c r="S15" t="s">
+        <v>18</v>
+      </c>
+      <c r="T15" t="s">
         <v>19</v>
       </c>
       <c r="U15">
@@ -2139,27 +2137,27 @@
       <c r="Y15">
         <v>1201</v>
       </c>
-      <c r="AB15" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="AC15" s="1" t="s">
+      <c r="AB15" t="s">
+        <v>115</v>
+      </c>
+      <c r="AC15" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="16" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C16" s="1" t="s">
+      <c r="A16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" t="s">
         <v>42</v>
       </c>
-      <c r="D16" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E16" s="1" t="s">
+      <c r="D16" t="s">
+        <v>18</v>
+      </c>
+      <c r="E16" t="s">
         <v>19</v>
       </c>
       <c r="F16">
@@ -2177,25 +2175,25 @@
       <c r="J16">
         <v>1059</v>
       </c>
-      <c r="M16" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="N16" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="P16" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q16" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="R16" s="1" t="s">
+      <c r="M16" t="s">
+        <v>115</v>
+      </c>
+      <c r="N16" t="s">
+        <v>115</v>
+      </c>
+      <c r="P16" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>20</v>
+      </c>
+      <c r="R16" t="s">
         <v>42</v>
       </c>
-      <c r="S16" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="T16" s="1" t="s">
+      <c r="S16" t="s">
+        <v>18</v>
+      </c>
+      <c r="T16" t="s">
         <v>19</v>
       </c>
       <c r="U16">
@@ -2213,27 +2211,27 @@
       <c r="Y16">
         <v>1169</v>
       </c>
-      <c r="AB16" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="AC16" s="1" t="s">
+      <c r="AB16" t="s">
+        <v>115</v>
+      </c>
+      <c r="AC16" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="17" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C17" s="1" t="s">
+      <c r="A17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" t="s">
         <v>43</v>
       </c>
-      <c r="D17" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E17" s="1" t="s">
+      <c r="D17" t="s">
+        <v>18</v>
+      </c>
+      <c r="E17" t="s">
         <v>19</v>
       </c>
       <c r="F17">
@@ -2251,25 +2249,25 @@
       <c r="J17">
         <v>1053</v>
       </c>
-      <c r="M17" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="N17" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="P17" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q17" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="R17" s="1" t="s">
+      <c r="M17" t="s">
+        <v>115</v>
+      </c>
+      <c r="N17" t="s">
+        <v>115</v>
+      </c>
+      <c r="P17" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>20</v>
+      </c>
+      <c r="R17" t="s">
         <v>43</v>
       </c>
-      <c r="S17" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="T17" s="1" t="s">
+      <c r="S17" t="s">
+        <v>18</v>
+      </c>
+      <c r="T17" t="s">
         <v>19</v>
       </c>
       <c r="U17">
@@ -2287,27 +2285,27 @@
       <c r="Y17">
         <v>1157</v>
       </c>
-      <c r="AB17" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="AC17" s="1" t="s">
+      <c r="AB17" t="s">
+        <v>115</v>
+      </c>
+      <c r="AC17" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="18" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B18" s="1" t="s">
+      <c r="A18" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" t="s">
         <v>44</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C18" t="s">
         <v>45</v>
       </c>
-      <c r="D18" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E18" s="1" t="s">
+      <c r="D18" t="s">
+        <v>18</v>
+      </c>
+      <c r="E18" t="s">
         <v>19</v>
       </c>
       <c r="F18">
@@ -2325,25 +2323,25 @@
       <c r="J18">
         <v>2922</v>
       </c>
-      <c r="M18" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="N18" s="1" t="s">
+      <c r="M18" t="s">
+        <v>115</v>
+      </c>
+      <c r="N18" t="s">
         <v>46</v>
       </c>
-      <c r="P18" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q18" s="1" t="s">
+      <c r="P18" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q18" t="s">
         <v>44</v>
       </c>
-      <c r="R18" s="1" t="s">
+      <c r="R18" t="s">
         <v>45</v>
       </c>
-      <c r="S18" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="T18" s="1" t="s">
+      <c r="S18" t="s">
+        <v>18</v>
+      </c>
+      <c r="T18" t="s">
         <v>19</v>
       </c>
       <c r="U18">
@@ -2361,27 +2359,27 @@
       <c r="Y18">
         <v>1469</v>
       </c>
-      <c r="AB18" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="AC18" s="1" t="s">
+      <c r="AB18" t="s">
+        <v>115</v>
+      </c>
+      <c r="AC18" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="19" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B19" s="1" t="s">
+      <c r="A19" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" t="s">
         <v>44</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="C19" t="s">
         <v>47</v>
       </c>
-      <c r="D19" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E19" s="1" t="s">
+      <c r="D19" t="s">
+        <v>18</v>
+      </c>
+      <c r="E19" t="s">
         <v>19</v>
       </c>
       <c r="F19">
@@ -2399,25 +2397,25 @@
       <c r="J19">
         <v>1239</v>
       </c>
-      <c r="M19" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="N19" s="1" t="s">
+      <c r="M19" t="s">
+        <v>115</v>
+      </c>
+      <c r="N19" t="s">
         <v>48</v>
       </c>
-      <c r="P19" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q19" s="1" t="s">
+      <c r="P19" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q19" t="s">
         <v>44</v>
       </c>
-      <c r="R19" s="1" t="s">
+      <c r="R19" t="s">
         <v>47</v>
       </c>
-      <c r="S19" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="T19" s="1" t="s">
+      <c r="S19" t="s">
+        <v>18</v>
+      </c>
+      <c r="T19" t="s">
         <v>19</v>
       </c>
       <c r="U19">
@@ -2435,27 +2433,27 @@
       <c r="Y19">
         <v>1361</v>
       </c>
-      <c r="AB19" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="AC19" s="1" t="s">
+      <c r="AB19" t="s">
+        <v>115</v>
+      </c>
+      <c r="AC19" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="20" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B20" s="1" t="s">
+      <c r="A20" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" t="s">
         <v>44</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="C20" t="s">
         <v>49</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="D20" t="s">
         <v>34</v>
       </c>
-      <c r="E20" s="1" t="s">
+      <c r="E20" t="s">
         <v>35</v>
       </c>
       <c r="F20">
@@ -2473,25 +2471,25 @@
       <c r="J20">
         <v>449</v>
       </c>
-      <c r="M20" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="N20" s="1" t="s">
+      <c r="M20" t="s">
+        <v>115</v>
+      </c>
+      <c r="N20" t="s">
         <v>26</v>
       </c>
-      <c r="P20" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q20" s="1" t="s">
+      <c r="P20" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q20" t="s">
         <v>44</v>
       </c>
-      <c r="R20" s="1" t="s">
+      <c r="R20" t="s">
         <v>49</v>
       </c>
-      <c r="S20" s="1" t="s">
+      <c r="S20" t="s">
         <v>116</v>
       </c>
-      <c r="T20" s="1" t="s">
+      <c r="T20" t="s">
         <v>117</v>
       </c>
       <c r="U20">
@@ -2509,27 +2507,27 @@
       <c r="Y20">
         <v>1892</v>
       </c>
-      <c r="AB20" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="AC20" s="1" t="s">
+      <c r="AB20" t="s">
+        <v>115</v>
+      </c>
+      <c r="AC20" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="21" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B21" s="1" t="s">
+      <c r="A21" t="s">
+        <v>15</v>
+      </c>
+      <c r="B21" t="s">
         <v>44</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="C21" t="s">
         <v>50</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="D21" t="s">
         <v>51</v>
       </c>
-      <c r="E21" s="1" t="s">
+      <c r="E21" t="s">
         <v>52</v>
       </c>
       <c r="F21">
@@ -2547,25 +2545,25 @@
       <c r="J21">
         <v>1283</v>
       </c>
-      <c r="M21" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="N21" s="1" t="s">
+      <c r="M21" t="s">
+        <v>115</v>
+      </c>
+      <c r="N21" t="s">
         <v>2</v>
       </c>
-      <c r="P21" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q21" s="1" t="s">
+      <c r="P21" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q21" t="s">
         <v>44</v>
       </c>
-      <c r="R21" s="1" t="s">
+      <c r="R21" t="s">
         <v>50</v>
       </c>
-      <c r="S21" s="1" t="s">
+      <c r="S21" t="s">
         <v>140</v>
       </c>
-      <c r="T21" s="1" t="s">
+      <c r="T21" t="s">
         <v>113</v>
       </c>
       <c r="U21">
@@ -2583,51 +2581,51 @@
       <c r="Y21">
         <v>1685</v>
       </c>
-      <c r="AB21" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="AC21" s="1" t="s">
+      <c r="AB21" t="s">
+        <v>115</v>
+      </c>
+      <c r="AC21" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="22" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B22" s="1" t="s">
+      <c r="A22" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22" t="s">
         <v>44</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="C22" t="s">
         <v>53</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="D22" t="s">
         <v>54</v>
       </c>
-      <c r="E22" s="1" t="s">
+      <c r="E22" t="s">
         <v>55</v>
       </c>
       <c r="F22">
         <v>0</v>
       </c>
-      <c r="M22" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="N22" s="1" t="s">
+      <c r="M22" t="s">
+        <v>115</v>
+      </c>
+      <c r="N22" t="s">
         <v>2</v>
       </c>
-      <c r="P22" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q22" s="1" t="s">
+      <c r="P22" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q22" t="s">
         <v>44</v>
       </c>
-      <c r="R22" s="1" t="s">
+      <c r="R22" t="s">
         <v>53</v>
       </c>
-      <c r="S22" s="1" t="s">
+      <c r="S22" t="s">
         <v>124</v>
       </c>
-      <c r="T22" s="1" t="s">
+      <c r="T22" t="s">
         <v>71</v>
       </c>
       <c r="U22">
@@ -2645,277 +2643,277 @@
       <c r="Y22">
         <v>3293</v>
       </c>
-      <c r="AB22" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="AC22" s="1" t="s">
+      <c r="AB22" t="s">
+        <v>115</v>
+      </c>
+      <c r="AC22" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="23" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B23" s="1" t="s">
+      <c r="A23" t="s">
+        <v>15</v>
+      </c>
+      <c r="B23" t="s">
         <v>44</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="C23" t="s">
         <v>56</v>
       </c>
-      <c r="D23" s="1" t="s">
+      <c r="D23" t="s">
         <v>54</v>
       </c>
-      <c r="E23" s="1" t="s">
+      <c r="E23" t="s">
         <v>55</v>
       </c>
       <c r="F23">
         <v>0</v>
       </c>
-      <c r="M23" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="N23" s="1" t="s">
+      <c r="M23" t="s">
+        <v>115</v>
+      </c>
+      <c r="N23" t="s">
         <v>2</v>
       </c>
-      <c r="P23" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q23" s="1" t="s">
+      <c r="P23" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q23" t="s">
         <v>44</v>
       </c>
-      <c r="R23" s="1" t="s">
+      <c r="R23" t="s">
         <v>56</v>
       </c>
-      <c r="S23" s="1" t="s">
+      <c r="S23" t="s">
         <v>54</v>
       </c>
-      <c r="T23" s="1" t="s">
+      <c r="T23" t="s">
         <v>55</v>
       </c>
       <c r="U23">
         <v>0</v>
       </c>
-      <c r="AB23" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="AC23" s="1" t="s">
+      <c r="AB23" t="s">
+        <v>115</v>
+      </c>
+      <c r="AC23" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B24" s="1" t="s">
+      <c r="A24" t="s">
+        <v>15</v>
+      </c>
+      <c r="B24" t="s">
         <v>44</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="C24" t="s">
         <v>57</v>
       </c>
-      <c r="D24" s="1" t="s">
+      <c r="D24" t="s">
         <v>54</v>
       </c>
-      <c r="E24" s="1" t="s">
+      <c r="E24" t="s">
         <v>55</v>
       </c>
       <c r="F24">
         <v>0</v>
       </c>
-      <c r="M24" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="N24" s="1" t="s">
+      <c r="M24" t="s">
+        <v>115</v>
+      </c>
+      <c r="N24" t="s">
         <v>2</v>
       </c>
-      <c r="P24" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q24" s="1" t="s">
+      <c r="P24" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q24" t="s">
         <v>44</v>
       </c>
-      <c r="R24" s="1" t="s">
+      <c r="R24" t="s">
         <v>57</v>
       </c>
-      <c r="S24" s="1" t="s">
+      <c r="S24" t="s">
         <v>54</v>
       </c>
-      <c r="T24" s="1" t="s">
+      <c r="T24" t="s">
         <v>55</v>
       </c>
       <c r="U24">
         <v>0</v>
       </c>
-      <c r="AB24" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="AC24" s="1" t="s">
+      <c r="AB24" t="s">
+        <v>115</v>
+      </c>
+      <c r="AC24" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B25" s="1" t="s">
+      <c r="A25" t="s">
+        <v>15</v>
+      </c>
+      <c r="B25" t="s">
         <v>44</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="C25" t="s">
         <v>58</v>
       </c>
-      <c r="D25" s="1" t="s">
+      <c r="D25" t="s">
         <v>54</v>
       </c>
-      <c r="E25" s="1" t="s">
+      <c r="E25" t="s">
         <v>55</v>
       </c>
       <c r="F25">
         <v>0</v>
       </c>
-      <c r="M25" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="N25" s="1" t="s">
+      <c r="M25" t="s">
+        <v>115</v>
+      </c>
+      <c r="N25" t="s">
         <v>2</v>
       </c>
-      <c r="P25" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q25" s="1" t="s">
+      <c r="P25" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q25" t="s">
         <v>44</v>
       </c>
-      <c r="R25" s="1" t="s">
+      <c r="R25" t="s">
         <v>58</v>
       </c>
-      <c r="S25" s="1" t="s">
+      <c r="S25" t="s">
         <v>54</v>
       </c>
-      <c r="T25" s="1" t="s">
+      <c r="T25" t="s">
         <v>55</v>
       </c>
       <c r="U25">
         <v>0</v>
       </c>
-      <c r="AB25" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="AC25" s="1" t="s">
+      <c r="AB25" t="s">
+        <v>115</v>
+      </c>
+      <c r="AC25" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B26" s="1" t="s">
+      <c r="A26" t="s">
+        <v>15</v>
+      </c>
+      <c r="B26" t="s">
         <v>44</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="C26" t="s">
         <v>59</v>
       </c>
-      <c r="D26" s="1" t="s">
+      <c r="D26" t="s">
         <v>54</v>
       </c>
-      <c r="E26" s="1" t="s">
+      <c r="E26" t="s">
         <v>55</v>
       </c>
       <c r="F26">
         <v>0</v>
       </c>
-      <c r="M26" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="N26" s="1" t="s">
+      <c r="M26" t="s">
+        <v>115</v>
+      </c>
+      <c r="N26" t="s">
         <v>2</v>
       </c>
-      <c r="P26" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q26" s="1" t="s">
+      <c r="P26" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q26" t="s">
         <v>44</v>
       </c>
-      <c r="R26" s="1" t="s">
+      <c r="R26" t="s">
         <v>59</v>
       </c>
-      <c r="S26" s="1" t="s">
+      <c r="S26" t="s">
         <v>54</v>
       </c>
-      <c r="T26" s="1" t="s">
+      <c r="T26" t="s">
         <v>55</v>
       </c>
       <c r="U26">
         <v>0</v>
       </c>
-      <c r="AB26" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="AC26" s="1" t="s">
+      <c r="AB26" t="s">
+        <v>115</v>
+      </c>
+      <c r="AC26" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B27" s="1" t="s">
+      <c r="A27" t="s">
+        <v>15</v>
+      </c>
+      <c r="B27" t="s">
         <v>44</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="C27" t="s">
         <v>60</v>
       </c>
-      <c r="D27" s="1" t="s">
+      <c r="D27" t="s">
         <v>54</v>
       </c>
-      <c r="E27" s="1" t="s">
+      <c r="E27" t="s">
         <v>55</v>
       </c>
       <c r="F27">
         <v>0</v>
       </c>
-      <c r="M27" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="N27" s="1" t="s">
+      <c r="M27" t="s">
+        <v>115</v>
+      </c>
+      <c r="N27" t="s">
         <v>2</v>
       </c>
-      <c r="P27" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q27" s="1" t="s">
+      <c r="P27" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q27" t="s">
         <v>44</v>
       </c>
-      <c r="R27" s="1" t="s">
+      <c r="R27" t="s">
         <v>60</v>
       </c>
-      <c r="S27" s="1" t="s">
+      <c r="S27" t="s">
         <v>54</v>
       </c>
-      <c r="T27" s="1" t="s">
+      <c r="T27" t="s">
         <v>55</v>
       </c>
       <c r="U27">
         <v>0</v>
       </c>
-      <c r="AB27" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="AC27" s="1" t="s">
+      <c r="AB27" t="s">
+        <v>115</v>
+      </c>
+      <c r="AC27" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="28" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B28" s="1" t="s">
+      <c r="A28" t="s">
+        <v>15</v>
+      </c>
+      <c r="B28" t="s">
         <v>61</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="C28" t="s">
         <v>62</v>
       </c>
-      <c r="D28" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E28" s="1" t="s">
+      <c r="D28" t="s">
+        <v>18</v>
+      </c>
+      <c r="E28" t="s">
         <v>19</v>
       </c>
       <c r="F28">
@@ -2933,25 +2931,25 @@
       <c r="J28">
         <v>1363</v>
       </c>
-      <c r="M28" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="N28" s="1" t="s">
+      <c r="M28" t="s">
+        <v>115</v>
+      </c>
+      <c r="N28" t="s">
         <v>46</v>
       </c>
-      <c r="P28" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q28" s="1" t="s">
+      <c r="P28" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q28" t="s">
         <v>61</v>
       </c>
-      <c r="R28" s="1" t="s">
+      <c r="R28" t="s">
         <v>62</v>
       </c>
-      <c r="S28" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="T28" s="1" t="s">
+      <c r="S28" t="s">
+        <v>18</v>
+      </c>
+      <c r="T28" t="s">
         <v>19</v>
       </c>
       <c r="U28">
@@ -2969,27 +2967,27 @@
       <c r="Y28">
         <v>1429</v>
       </c>
-      <c r="AB28" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="AC28" s="1" t="s">
+      <c r="AB28" t="s">
+        <v>115</v>
+      </c>
+      <c r="AC28" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="29" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B29" s="1" t="s">
+      <c r="A29" t="s">
+        <v>15</v>
+      </c>
+      <c r="B29" t="s">
         <v>61</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="C29" t="s">
         <v>63</v>
       </c>
-      <c r="D29" s="1" t="s">
+      <c r="D29" t="s">
         <v>118</v>
       </c>
-      <c r="E29" s="1" t="s">
+      <c r="E29" t="s">
         <v>119</v>
       </c>
       <c r="F29">
@@ -3007,25 +3005,25 @@
       <c r="J29">
         <v>2714</v>
       </c>
-      <c r="M29" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="N29" s="1" t="s">
+      <c r="M29" t="s">
+        <v>115</v>
+      </c>
+      <c r="N29" t="s">
         <v>46</v>
       </c>
-      <c r="P29" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q29" s="1" t="s">
+      <c r="P29" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q29" t="s">
         <v>61</v>
       </c>
-      <c r="R29" s="1" t="s">
+      <c r="R29" t="s">
         <v>63</v>
       </c>
-      <c r="S29" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="T29" s="1" t="s">
+      <c r="S29" t="s">
+        <v>18</v>
+      </c>
+      <c r="T29" t="s">
         <v>19</v>
       </c>
       <c r="U29">
@@ -3043,27 +3041,27 @@
       <c r="Y29">
         <v>1558</v>
       </c>
-      <c r="AB29" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="AC29" s="1" t="s">
+      <c r="AB29" t="s">
+        <v>115</v>
+      </c>
+      <c r="AC29" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="30" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B30" s="1" t="s">
+      <c r="A30" t="s">
+        <v>15</v>
+      </c>
+      <c r="B30" t="s">
         <v>61</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="C30" t="s">
         <v>64</v>
       </c>
-      <c r="D30" s="1" t="s">
+      <c r="D30" t="s">
         <v>38</v>
       </c>
-      <c r="E30" s="1" t="s">
+      <c r="E30" t="s">
         <v>39</v>
       </c>
       <c r="F30">
@@ -3081,25 +3079,25 @@
       <c r="J30">
         <v>4711</v>
       </c>
-      <c r="M30" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="N30" s="1" t="s">
+      <c r="M30" t="s">
+        <v>115</v>
+      </c>
+      <c r="N30" t="s">
         <v>26</v>
       </c>
-      <c r="P30" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q30" s="1" t="s">
+      <c r="P30" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q30" t="s">
         <v>61</v>
       </c>
-      <c r="R30" s="1" t="s">
+      <c r="R30" t="s">
         <v>64</v>
       </c>
-      <c r="S30" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="T30" s="1" t="s">
+      <c r="S30" t="s">
+        <v>18</v>
+      </c>
+      <c r="T30" t="s">
         <v>19</v>
       </c>
       <c r="U30">
@@ -3117,51 +3115,51 @@
       <c r="Y30">
         <v>2175</v>
       </c>
-      <c r="AB30" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="AC30" s="1" t="s">
+      <c r="AB30" t="s">
+        <v>115</v>
+      </c>
+      <c r="AC30" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="31" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B31" s="1" t="s">
+      <c r="A31" t="s">
+        <v>15</v>
+      </c>
+      <c r="B31" t="s">
         <v>61</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="C31" t="s">
         <v>65</v>
       </c>
-      <c r="D31" s="1" t="s">
+      <c r="D31" t="s">
         <v>54</v>
       </c>
-      <c r="E31" s="1" t="s">
+      <c r="E31" t="s">
         <v>55</v>
       </c>
       <c r="F31">
         <v>0</v>
       </c>
-      <c r="M31" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="N31" s="1" t="s">
+      <c r="M31" t="s">
+        <v>115</v>
+      </c>
+      <c r="N31" t="s">
         <v>2</v>
       </c>
-      <c r="P31" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q31" s="1" t="s">
+      <c r="P31" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q31" t="s">
         <v>61</v>
       </c>
-      <c r="R31" s="1" t="s">
+      <c r="R31" t="s">
         <v>65</v>
       </c>
-      <c r="S31" s="1" t="s">
+      <c r="S31" t="s">
         <v>138</v>
       </c>
-      <c r="T31" s="1" t="s">
+      <c r="T31" t="s">
         <v>139</v>
       </c>
       <c r="U31">
@@ -3179,27 +3177,27 @@
       <c r="Y31">
         <v>3221</v>
       </c>
-      <c r="AB31" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="AC31" s="1" t="s">
+      <c r="AB31" t="s">
+        <v>115</v>
+      </c>
+      <c r="AC31" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="32" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B32" s="1" t="s">
+      <c r="A32" t="s">
+        <v>15</v>
+      </c>
+      <c r="B32" t="s">
         <v>61</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="C32" t="s">
         <v>66</v>
       </c>
-      <c r="D32" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E32" s="1" t="s">
+      <c r="D32" t="s">
+        <v>18</v>
+      </c>
+      <c r="E32" t="s">
         <v>19</v>
       </c>
       <c r="F32">
@@ -3217,25 +3215,25 @@
       <c r="J32">
         <v>1098</v>
       </c>
-      <c r="M32" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="N32" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="P32" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q32" s="1" t="s">
+      <c r="M32" t="s">
+        <v>115</v>
+      </c>
+      <c r="N32" t="s">
+        <v>115</v>
+      </c>
+      <c r="P32" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q32" t="s">
         <v>61</v>
       </c>
-      <c r="R32" s="1" t="s">
+      <c r="R32" t="s">
         <v>66</v>
       </c>
-      <c r="S32" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="T32" s="1" t="s">
+      <c r="S32" t="s">
+        <v>18</v>
+      </c>
+      <c r="T32" t="s">
         <v>19</v>
       </c>
       <c r="U32">
@@ -3253,27 +3251,27 @@
       <c r="Y32">
         <v>1258</v>
       </c>
-      <c r="AB32" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="AC32" s="1" t="s">
+      <c r="AB32" t="s">
+        <v>115</v>
+      </c>
+      <c r="AC32" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="33" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B33" s="1" t="s">
+      <c r="A33" t="s">
+        <v>15</v>
+      </c>
+      <c r="B33" t="s">
         <v>61</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C33" t="s">
         <v>67</v>
       </c>
-      <c r="D33" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E33" s="1" t="s">
+      <c r="D33" t="s">
+        <v>18</v>
+      </c>
+      <c r="E33" t="s">
         <v>19</v>
       </c>
       <c r="F33">
@@ -3291,25 +3289,25 @@
       <c r="J33">
         <v>1106</v>
       </c>
-      <c r="M33" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="N33" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="P33" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q33" s="1" t="s">
+      <c r="M33" t="s">
+        <v>115</v>
+      </c>
+      <c r="N33" t="s">
+        <v>115</v>
+      </c>
+      <c r="P33" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q33" t="s">
         <v>61</v>
       </c>
-      <c r="R33" s="1" t="s">
+      <c r="R33" t="s">
         <v>67</v>
       </c>
-      <c r="S33" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="T33" s="1" t="s">
+      <c r="S33" t="s">
+        <v>18</v>
+      </c>
+      <c r="T33" t="s">
         <v>19</v>
       </c>
       <c r="U33">
@@ -3327,27 +3325,27 @@
       <c r="Y33">
         <v>1268</v>
       </c>
-      <c r="AB33" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="AC33" s="1" t="s">
+      <c r="AB33" t="s">
+        <v>115</v>
+      </c>
+      <c r="AC33" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="34" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B34" s="1" t="s">
+      <c r="A34" t="s">
+        <v>15</v>
+      </c>
+      <c r="B34" t="s">
         <v>61</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="C34" t="s">
         <v>68</v>
       </c>
-      <c r="D34" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E34" s="1" t="s">
+      <c r="D34" t="s">
+        <v>18</v>
+      </c>
+      <c r="E34" t="s">
         <v>19</v>
       </c>
       <c r="F34">
@@ -3365,25 +3363,25 @@
       <c r="J34">
         <v>1333</v>
       </c>
-      <c r="M34" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="N34" s="1" t="s">
+      <c r="M34" t="s">
+        <v>115</v>
+      </c>
+      <c r="N34" t="s">
         <v>46</v>
       </c>
-      <c r="P34" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q34" s="1" t="s">
+      <c r="P34" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q34" t="s">
         <v>61</v>
       </c>
-      <c r="R34" s="1" t="s">
+      <c r="R34" t="s">
         <v>68</v>
       </c>
-      <c r="S34" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="T34" s="1" t="s">
+      <c r="S34" t="s">
+        <v>18</v>
+      </c>
+      <c r="T34" t="s">
         <v>19</v>
       </c>
       <c r="U34">
@@ -3401,27 +3399,27 @@
       <c r="Y34">
         <v>1451</v>
       </c>
-      <c r="AB34" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="AC34" s="1" t="s">
+      <c r="AB34" t="s">
+        <v>115</v>
+      </c>
+      <c r="AC34" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="35" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B35" s="1" t="s">
+      <c r="A35" t="s">
+        <v>15</v>
+      </c>
+      <c r="B35" t="s">
         <v>61</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="C35" t="s">
         <v>69</v>
       </c>
-      <c r="D35" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E35" s="1" t="s">
+      <c r="D35" t="s">
+        <v>18</v>
+      </c>
+      <c r="E35" t="s">
         <v>19</v>
       </c>
       <c r="F35">
@@ -3439,25 +3437,25 @@
       <c r="J35">
         <v>1023</v>
       </c>
-      <c r="M35" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="N35" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="P35" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q35" s="1" t="s">
+      <c r="M35" t="s">
+        <v>115</v>
+      </c>
+      <c r="N35" t="s">
+        <v>115</v>
+      </c>
+      <c r="P35" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q35" t="s">
         <v>61</v>
       </c>
-      <c r="R35" s="1" t="s">
+      <c r="R35" t="s">
         <v>69</v>
       </c>
-      <c r="S35" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="T35" s="1" t="s">
+      <c r="S35" t="s">
+        <v>18</v>
+      </c>
+      <c r="T35" t="s">
         <v>19</v>
       </c>
       <c r="U35">
@@ -3475,27 +3473,27 @@
       <c r="Y35">
         <v>1129</v>
       </c>
-      <c r="AB35" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="AC35" s="1" t="s">
+      <c r="AB35" t="s">
+        <v>115</v>
+      </c>
+      <c r="AC35" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="36" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B36" s="1" t="s">
+      <c r="A36" t="s">
+        <v>15</v>
+      </c>
+      <c r="B36" t="s">
         <v>61</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="C36" t="s">
         <v>70</v>
       </c>
-      <c r="D36" s="1" t="s">
+      <c r="D36" t="s">
         <v>124</v>
       </c>
-      <c r="E36" s="1" t="s">
+      <c r="E36" t="s">
         <v>71</v>
       </c>
       <c r="F36">
@@ -3513,25 +3511,25 @@
       <c r="J36">
         <v>2335</v>
       </c>
-      <c r="M36" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="N36" s="1" t="s">
+      <c r="M36" t="s">
+        <v>115</v>
+      </c>
+      <c r="N36" t="s">
         <v>26</v>
       </c>
-      <c r="P36" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q36" s="1" t="s">
+      <c r="P36" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q36" t="s">
         <v>61</v>
       </c>
-      <c r="R36" s="1" t="s">
+      <c r="R36" t="s">
         <v>70</v>
       </c>
-      <c r="S36" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="T36" s="1" t="s">
+      <c r="S36" t="s">
+        <v>18</v>
+      </c>
+      <c r="T36" t="s">
         <v>19</v>
       </c>
       <c r="U36">
@@ -3549,27 +3547,27 @@
       <c r="Y36">
         <v>1619</v>
       </c>
-      <c r="AB36" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="AC36" s="1" t="s">
+      <c r="AB36" t="s">
+        <v>115</v>
+      </c>
+      <c r="AC36" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="37" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B37" s="1" t="s">
+      <c r="A37" t="s">
+        <v>15</v>
+      </c>
+      <c r="B37" t="s">
         <v>61</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="C37" t="s">
         <v>72</v>
       </c>
-      <c r="D37" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E37" s="1" t="s">
+      <c r="D37" t="s">
+        <v>18</v>
+      </c>
+      <c r="E37" t="s">
         <v>19</v>
       </c>
       <c r="F37">
@@ -3587,25 +3585,25 @@
       <c r="J37">
         <v>939</v>
       </c>
-      <c r="M37" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="N37" s="1" t="s">
+      <c r="M37" t="s">
+        <v>115</v>
+      </c>
+      <c r="N37" t="s">
         <v>32</v>
       </c>
-      <c r="P37" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q37" s="1" t="s">
+      <c r="P37" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q37" t="s">
         <v>61</v>
       </c>
-      <c r="R37" s="1" t="s">
+      <c r="R37" t="s">
         <v>72</v>
       </c>
-      <c r="S37" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="T37" s="1" t="s">
+      <c r="S37" t="s">
+        <v>18</v>
+      </c>
+      <c r="T37" t="s">
         <v>19</v>
       </c>
       <c r="U37">
@@ -3623,51 +3621,51 @@
       <c r="Y37">
         <v>103</v>
       </c>
-      <c r="AB37" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="AC37" s="1" t="s">
+      <c r="AB37" t="s">
+        <v>115</v>
+      </c>
+      <c r="AC37" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="38" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B38" s="1" t="s">
+      <c r="A38" t="s">
+        <v>15</v>
+      </c>
+      <c r="B38" t="s">
         <v>61</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="C38" t="s">
         <v>73</v>
       </c>
-      <c r="D38" s="1" t="s">
+      <c r="D38" t="s">
         <v>54</v>
       </c>
-      <c r="E38" s="1" t="s">
+      <c r="E38" t="s">
         <v>55</v>
       </c>
       <c r="F38">
         <v>0</v>
       </c>
-      <c r="M38" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="N38" s="1" t="s">
+      <c r="M38" t="s">
+        <v>115</v>
+      </c>
+      <c r="N38" t="s">
         <v>2</v>
       </c>
-      <c r="P38" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q38" s="1" t="s">
+      <c r="P38" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q38" t="s">
         <v>61</v>
       </c>
-      <c r="R38" s="1" t="s">
+      <c r="R38" t="s">
         <v>73</v>
       </c>
-      <c r="S38" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="T38" s="1" t="s">
+      <c r="S38" t="s">
+        <v>18</v>
+      </c>
+      <c r="T38" t="s">
         <v>19</v>
       </c>
       <c r="U38">
@@ -3685,27 +3683,27 @@
       <c r="Y38">
         <v>3344</v>
       </c>
-      <c r="AB38" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="AC38" s="1" t="s">
+      <c r="AB38" t="s">
+        <v>115</v>
+      </c>
+      <c r="AC38" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="39" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B39" s="1" t="s">
+      <c r="A39" t="s">
+        <v>15</v>
+      </c>
+      <c r="B39" t="s">
         <v>61</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="C39" t="s">
         <v>74</v>
       </c>
-      <c r="D39" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E39" s="1" t="s">
+      <c r="D39" t="s">
+        <v>18</v>
+      </c>
+      <c r="E39" t="s">
         <v>19</v>
       </c>
       <c r="F39">
@@ -3723,25 +3721,25 @@
       <c r="J39">
         <v>856</v>
       </c>
-      <c r="M39" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="N39" s="1" t="s">
+      <c r="M39" t="s">
+        <v>115</v>
+      </c>
+      <c r="N39" t="s">
         <v>32</v>
       </c>
-      <c r="P39" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q39" s="1" t="s">
+      <c r="P39" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q39" t="s">
         <v>61</v>
       </c>
-      <c r="R39" s="1" t="s">
+      <c r="R39" t="s">
         <v>74</v>
       </c>
-      <c r="S39" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="T39" s="1" t="s">
+      <c r="S39" t="s">
+        <v>18</v>
+      </c>
+      <c r="T39" t="s">
         <v>19</v>
       </c>
       <c r="U39">
@@ -3759,51 +3757,51 @@
       <c r="Y39">
         <v>934</v>
       </c>
-      <c r="AB39" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="AC39" s="1" t="s">
+      <c r="AB39" t="s">
+        <v>115</v>
+      </c>
+      <c r="AC39" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="40" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B40" s="1" t="s">
+      <c r="A40" t="s">
+        <v>15</v>
+      </c>
+      <c r="B40" t="s">
         <v>61</v>
       </c>
-      <c r="C40" s="1" t="s">
+      <c r="C40" t="s">
         <v>75</v>
       </c>
-      <c r="D40" s="1" t="s">
+      <c r="D40" t="s">
         <v>54</v>
       </c>
-      <c r="E40" s="1" t="s">
+      <c r="E40" t="s">
         <v>55</v>
       </c>
       <c r="F40">
         <v>0</v>
       </c>
-      <c r="M40" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="N40" s="1" t="s">
+      <c r="M40" t="s">
+        <v>115</v>
+      </c>
+      <c r="N40" t="s">
         <v>2</v>
       </c>
-      <c r="P40" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q40" s="1" t="s">
+      <c r="P40" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q40" t="s">
         <v>61</v>
       </c>
-      <c r="R40" s="1" t="s">
+      <c r="R40" t="s">
         <v>75</v>
       </c>
-      <c r="S40" s="1" t="s">
+      <c r="S40" t="s">
         <v>122</v>
       </c>
-      <c r="T40" s="1" t="s">
+      <c r="T40" t="s">
         <v>123</v>
       </c>
       <c r="U40">
@@ -3821,27 +3819,27 @@
       <c r="Y40">
         <v>9042</v>
       </c>
-      <c r="AB40" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="AC40" s="1" t="s">
+      <c r="AB40" t="s">
+        <v>115</v>
+      </c>
+      <c r="AC40" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="41" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B41" s="1" t="s">
+      <c r="A41" t="s">
+        <v>15</v>
+      </c>
+      <c r="B41" t="s">
         <v>61</v>
       </c>
-      <c r="C41" s="1" t="s">
+      <c r="C41" t="s">
         <v>76</v>
       </c>
-      <c r="D41" s="1" t="s">
+      <c r="D41" t="s">
         <v>116</v>
       </c>
-      <c r="E41" s="1" t="s">
+      <c r="E41" t="s">
         <v>117</v>
       </c>
       <c r="F41">
@@ -3859,25 +3857,25 @@
       <c r="J41">
         <v>809</v>
       </c>
-      <c r="M41" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="N41" s="1" t="s">
+      <c r="M41" t="s">
+        <v>115</v>
+      </c>
+      <c r="N41" t="s">
         <v>32</v>
       </c>
-      <c r="P41" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q41" s="1" t="s">
+      <c r="P41" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q41" t="s">
         <v>61</v>
       </c>
-      <c r="R41" s="1" t="s">
+      <c r="R41" t="s">
         <v>76</v>
       </c>
-      <c r="S41" s="1" t="s">
+      <c r="S41" t="s">
         <v>138</v>
       </c>
-      <c r="T41" s="1" t="s">
+      <c r="T41" t="s">
         <v>139</v>
       </c>
       <c r="U41">
@@ -3895,77 +3893,77 @@
       <c r="Y41">
         <v>2929</v>
       </c>
-      <c r="AB41" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="AC41" s="1" t="s">
+      <c r="AB41" t="s">
+        <v>115</v>
+      </c>
+      <c r="AC41" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="42" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B42" s="1" t="s">
+      <c r="A42" t="s">
+        <v>15</v>
+      </c>
+      <c r="B42" t="s">
         <v>61</v>
       </c>
-      <c r="C42" s="1" t="s">
+      <c r="C42" t="s">
         <v>77</v>
       </c>
-      <c r="D42" s="1" t="s">
+      <c r="D42" t="s">
         <v>54</v>
       </c>
-      <c r="E42" s="1" t="s">
+      <c r="E42" t="s">
         <v>55</v>
       </c>
       <c r="F42">
         <v>0</v>
       </c>
-      <c r="M42" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="N42" s="1" t="s">
+      <c r="M42" t="s">
+        <v>115</v>
+      </c>
+      <c r="N42" t="s">
         <v>2</v>
       </c>
-      <c r="P42" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q42" s="1" t="s">
+      <c r="P42" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q42" t="s">
         <v>61</v>
       </c>
-      <c r="R42" s="1" t="s">
+      <c r="R42" t="s">
         <v>77</v>
       </c>
-      <c r="S42" s="1" t="s">
+      <c r="S42" t="s">
         <v>54</v>
       </c>
-      <c r="T42" s="1" t="s">
+      <c r="T42" t="s">
         <v>55</v>
       </c>
       <c r="U42">
         <v>0</v>
       </c>
-      <c r="AB42" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="AC42" s="1" t="s">
+      <c r="AB42" t="s">
+        <v>115</v>
+      </c>
+      <c r="AC42" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="43" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B43" s="1" t="s">
+      <c r="A43" t="s">
+        <v>15</v>
+      </c>
+      <c r="B43" t="s">
         <v>61</v>
       </c>
-      <c r="C43" s="1" t="s">
+      <c r="C43" t="s">
         <v>78</v>
       </c>
-      <c r="D43" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E43" s="1" t="s">
+      <c r="D43" t="s">
+        <v>18</v>
+      </c>
+      <c r="E43" t="s">
         <v>19</v>
       </c>
       <c r="F43">
@@ -3983,25 +3981,25 @@
       <c r="J43">
         <v>1172</v>
       </c>
-      <c r="M43" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="N43" s="1" t="s">
+      <c r="M43" t="s">
+        <v>115</v>
+      </c>
+      <c r="N43" t="s">
         <v>32</v>
       </c>
-      <c r="P43" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q43" s="1" t="s">
+      <c r="P43" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q43" t="s">
         <v>61</v>
       </c>
-      <c r="R43" s="1" t="s">
+      <c r="R43" t="s">
         <v>78</v>
       </c>
-      <c r="S43" s="1" t="s">
+      <c r="S43" t="s">
         <v>138</v>
       </c>
-      <c r="T43" s="1" t="s">
+      <c r="T43" t="s">
         <v>139</v>
       </c>
       <c r="U43">
@@ -4019,101 +4017,101 @@
       <c r="Y43">
         <v>99</v>
       </c>
-      <c r="AB43" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="AC43" s="1" t="s">
+      <c r="AB43" t="s">
+        <v>115</v>
+      </c>
+      <c r="AC43" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="44" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B44" s="1" t="s">
+      <c r="A44" t="s">
+        <v>15</v>
+      </c>
+      <c r="B44" t="s">
         <v>61</v>
       </c>
-      <c r="C44" s="1" t="s">
+      <c r="C44" t="s">
         <v>79</v>
       </c>
-      <c r="D44" s="1" t="s">
+      <c r="D44" t="s">
         <v>54</v>
       </c>
-      <c r="E44" s="1" t="s">
+      <c r="E44" t="s">
         <v>55</v>
       </c>
       <c r="F44">
         <v>0</v>
       </c>
-      <c r="M44" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="N44" s="1" t="s">
+      <c r="M44" t="s">
+        <v>115</v>
+      </c>
+      <c r="N44" t="s">
         <v>2</v>
       </c>
-      <c r="P44" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q44" s="1" t="s">
+      <c r="P44" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q44" t="s">
         <v>61</v>
       </c>
-      <c r="R44" s="1" t="s">
+      <c r="R44" t="s">
         <v>79</v>
       </c>
-      <c r="S44" s="1" t="s">
+      <c r="S44" t="s">
         <v>54</v>
       </c>
-      <c r="T44" s="1" t="s">
+      <c r="T44" t="s">
         <v>55</v>
       </c>
       <c r="U44">
         <v>0</v>
       </c>
-      <c r="AB44" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="AC44" s="1" t="s">
+      <c r="AB44" t="s">
+        <v>115</v>
+      </c>
+      <c r="AC44" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="45" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B45" s="1" t="s">
+      <c r="A45" t="s">
+        <v>15</v>
+      </c>
+      <c r="B45" t="s">
         <v>61</v>
       </c>
-      <c r="C45" s="1" t="s">
+      <c r="C45" t="s">
         <v>80</v>
       </c>
-      <c r="D45" s="1" t="s">
+      <c r="D45" t="s">
         <v>54</v>
       </c>
-      <c r="E45" s="1" t="s">
+      <c r="E45" t="s">
         <v>55</v>
       </c>
       <c r="F45">
         <v>0</v>
       </c>
-      <c r="M45" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="N45" s="1" t="s">
+      <c r="M45" t="s">
+        <v>115</v>
+      </c>
+      <c r="N45" t="s">
         <v>2</v>
       </c>
-      <c r="P45" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q45" s="1" t="s">
+      <c r="P45" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q45" t="s">
         <v>61</v>
       </c>
-      <c r="R45" s="1" t="s">
+      <c r="R45" t="s">
         <v>80</v>
       </c>
-      <c r="S45" s="1" t="s">
+      <c r="S45" t="s">
         <v>34</v>
       </c>
-      <c r="T45" s="1" t="s">
+      <c r="T45" t="s">
         <v>35</v>
       </c>
       <c r="U45">
@@ -4131,27 +4129,27 @@
       <c r="Y45">
         <v>3351</v>
       </c>
-      <c r="AB45" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="AC45" s="1" t="s">
+      <c r="AB45" t="s">
+        <v>115</v>
+      </c>
+      <c r="AC45" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="46" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B46" s="1" t="s">
+      <c r="A46" t="s">
+        <v>15</v>
+      </c>
+      <c r="B46" t="s">
         <v>81</v>
       </c>
-      <c r="C46" s="1" t="s">
+      <c r="C46" t="s">
         <v>82</v>
       </c>
-      <c r="D46" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E46" s="1" t="s">
+      <c r="D46" t="s">
+        <v>18</v>
+      </c>
+      <c r="E46" t="s">
         <v>19</v>
       </c>
       <c r="F46">
@@ -4169,25 +4167,25 @@
       <c r="J46">
         <v>1084</v>
       </c>
-      <c r="M46" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="N46" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="P46" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q46" s="1" t="s">
+      <c r="M46" t="s">
+        <v>115</v>
+      </c>
+      <c r="N46" t="s">
+        <v>115</v>
+      </c>
+      <c r="P46" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q46" t="s">
         <v>81</v>
       </c>
-      <c r="R46" s="1" t="s">
+      <c r="R46" t="s">
         <v>82</v>
       </c>
-      <c r="S46" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="T46" s="1" t="s">
+      <c r="S46" t="s">
+        <v>18</v>
+      </c>
+      <c r="T46" t="s">
         <v>19</v>
       </c>
       <c r="U46">
@@ -4205,27 +4203,27 @@
       <c r="Y46">
         <v>1377</v>
       </c>
-      <c r="AB46" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="AC46" s="1" t="s">
+      <c r="AB46" t="s">
+        <v>115</v>
+      </c>
+      <c r="AC46" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="47" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B47" s="1" t="s">
+      <c r="A47" t="s">
+        <v>15</v>
+      </c>
+      <c r="B47" t="s">
         <v>81</v>
       </c>
-      <c r="C47" s="1" t="s">
+      <c r="C47" t="s">
         <v>83</v>
       </c>
-      <c r="D47" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E47" s="1" t="s">
+      <c r="D47" t="s">
+        <v>18</v>
+      </c>
+      <c r="E47" t="s">
         <v>19</v>
       </c>
       <c r="F47">
@@ -4243,25 +4241,25 @@
       <c r="J47">
         <v>1089</v>
       </c>
-      <c r="M47" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="N47" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="P47" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q47" s="1" t="s">
+      <c r="M47" t="s">
+        <v>115</v>
+      </c>
+      <c r="N47" t="s">
+        <v>115</v>
+      </c>
+      <c r="P47" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q47" t="s">
         <v>81</v>
       </c>
-      <c r="R47" s="1" t="s">
+      <c r="R47" t="s">
         <v>83</v>
       </c>
-      <c r="S47" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="T47" s="1" t="s">
+      <c r="S47" t="s">
+        <v>18</v>
+      </c>
+      <c r="T47" t="s">
         <v>19</v>
       </c>
       <c r="U47">
@@ -4279,27 +4277,27 @@
       <c r="Y47">
         <v>14</v>
       </c>
-      <c r="AB47" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="AC47" s="1" t="s">
+      <c r="AB47" t="s">
+        <v>115</v>
+      </c>
+      <c r="AC47" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="48" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A48" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B48" s="1" t="s">
+      <c r="A48" t="s">
+        <v>15</v>
+      </c>
+      <c r="B48" t="s">
         <v>81</v>
       </c>
-      <c r="C48" s="1" t="s">
+      <c r="C48" t="s">
         <v>84</v>
       </c>
-      <c r="D48" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E48" s="1" t="s">
+      <c r="D48" t="s">
+        <v>18</v>
+      </c>
+      <c r="E48" t="s">
         <v>19</v>
       </c>
       <c r="F48">
@@ -4317,25 +4315,25 @@
       <c r="J48">
         <v>116</v>
       </c>
-      <c r="M48" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="N48" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="P48" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q48" s="1" t="s">
+      <c r="M48" t="s">
+        <v>115</v>
+      </c>
+      <c r="N48" t="s">
+        <v>115</v>
+      </c>
+      <c r="P48" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q48" t="s">
         <v>81</v>
       </c>
-      <c r="R48" s="1" t="s">
+      <c r="R48" t="s">
         <v>84</v>
       </c>
-      <c r="S48" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="T48" s="1" t="s">
+      <c r="S48" t="s">
+        <v>18</v>
+      </c>
+      <c r="T48" t="s">
         <v>19</v>
       </c>
       <c r="U48">
@@ -4353,27 +4351,27 @@
       <c r="Y48">
         <v>1372</v>
       </c>
-      <c r="AB48" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="AC48" s="1" t="s">
+      <c r="AB48" t="s">
+        <v>115</v>
+      </c>
+      <c r="AC48" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="49" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A49" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B49" s="1" t="s">
+      <c r="A49" t="s">
+        <v>15</v>
+      </c>
+      <c r="B49" t="s">
         <v>81</v>
       </c>
-      <c r="C49" s="1" t="s">
+      <c r="C49" t="s">
         <v>85</v>
       </c>
-      <c r="D49" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E49" s="1" t="s">
+      <c r="D49" t="s">
+        <v>18</v>
+      </c>
+      <c r="E49" t="s">
         <v>19</v>
       </c>
       <c r="F49">
@@ -4391,25 +4389,25 @@
       <c r="J49">
         <v>1965</v>
       </c>
-      <c r="M49" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="N49" s="1" t="s">
+      <c r="M49" t="s">
+        <v>115</v>
+      </c>
+      <c r="N49" t="s">
         <v>46</v>
       </c>
-      <c r="P49" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q49" s="1" t="s">
+      <c r="P49" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q49" t="s">
         <v>81</v>
       </c>
-      <c r="R49" s="1" t="s">
+      <c r="R49" t="s">
         <v>85</v>
       </c>
-      <c r="S49" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="T49" s="1" t="s">
+      <c r="S49" t="s">
+        <v>18</v>
+      </c>
+      <c r="T49" t="s">
         <v>19</v>
       </c>
       <c r="U49">
@@ -4427,27 +4425,27 @@
       <c r="Y49">
         <v>1503</v>
       </c>
-      <c r="AB49" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="AC49" s="1" t="s">
+      <c r="AB49" t="s">
+        <v>115</v>
+      </c>
+      <c r="AC49" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="50" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A50" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B50" s="1" t="s">
+      <c r="A50" t="s">
+        <v>15</v>
+      </c>
+      <c r="B50" t="s">
         <v>81</v>
       </c>
-      <c r="C50" s="1" t="s">
+      <c r="C50" t="s">
         <v>86</v>
       </c>
-      <c r="D50" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E50" s="1" t="s">
+      <c r="D50" t="s">
+        <v>18</v>
+      </c>
+      <c r="E50" t="s">
         <v>19</v>
       </c>
       <c r="F50">
@@ -4465,25 +4463,25 @@
       <c r="J50">
         <v>2384</v>
       </c>
-      <c r="M50" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="N50" s="1" t="s">
+      <c r="M50" t="s">
+        <v>115</v>
+      </c>
+      <c r="N50" t="s">
         <v>46</v>
       </c>
-      <c r="P50" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q50" s="1" t="s">
+      <c r="P50" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q50" t="s">
         <v>81</v>
       </c>
-      <c r="R50" s="1" t="s">
+      <c r="R50" t="s">
         <v>86</v>
       </c>
-      <c r="S50" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="T50" s="1" t="s">
+      <c r="S50" t="s">
+        <v>18</v>
+      </c>
+      <c r="T50" t="s">
         <v>19</v>
       </c>
       <c r="U50">
@@ -4501,51 +4499,51 @@
       <c r="Y50">
         <v>1902</v>
       </c>
-      <c r="AB50" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="AC50" s="1" t="s">
+      <c r="AB50" t="s">
+        <v>115</v>
+      </c>
+      <c r="AC50" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="51" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A51" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B51" s="1" t="s">
+      <c r="A51" t="s">
+        <v>15</v>
+      </c>
+      <c r="B51" t="s">
         <v>81</v>
       </c>
-      <c r="C51" s="1" t="s">
+      <c r="C51" t="s">
         <v>87</v>
       </c>
-      <c r="D51" s="1" t="s">
+      <c r="D51" t="s">
         <v>54</v>
       </c>
-      <c r="E51" s="1" t="s">
+      <c r="E51" t="s">
         <v>55</v>
       </c>
       <c r="F51">
         <v>0</v>
       </c>
-      <c r="M51" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="N51" s="1" t="s">
+      <c r="M51" t="s">
+        <v>115</v>
+      </c>
+      <c r="N51" t="s">
         <v>2</v>
       </c>
-      <c r="P51" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q51" s="1" t="s">
+      <c r="P51" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q51" t="s">
         <v>81</v>
       </c>
-      <c r="R51" s="1" t="s">
+      <c r="R51" t="s">
         <v>87</v>
       </c>
-      <c r="S51" s="1" t="s">
+      <c r="S51" t="s">
         <v>138</v>
       </c>
-      <c r="T51" s="1" t="s">
+      <c r="T51" t="s">
         <v>139</v>
       </c>
       <c r="U51">
@@ -4563,27 +4561,27 @@
       <c r="Y51">
         <v>1421</v>
       </c>
-      <c r="AB51" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="AC51" s="1" t="s">
+      <c r="AB51" t="s">
+        <v>115</v>
+      </c>
+      <c r="AC51" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="52" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A52" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B52" s="1" t="s">
+      <c r="A52" t="s">
+        <v>15</v>
+      </c>
+      <c r="B52" t="s">
         <v>88</v>
       </c>
-      <c r="C52" s="1" t="s">
+      <c r="C52" t="s">
         <v>89</v>
       </c>
-      <c r="D52" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E52" s="1" t="s">
+      <c r="D52" t="s">
+        <v>18</v>
+      </c>
+      <c r="E52" t="s">
         <v>19</v>
       </c>
       <c r="F52">
@@ -4601,25 +4599,25 @@
       <c r="J52">
         <v>1173</v>
       </c>
-      <c r="M52" s="1" t="s">
+      <c r="M52" t="s">
         <v>125</v>
       </c>
-      <c r="N52" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="P52" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q52" s="1" t="s">
+      <c r="N52" t="s">
+        <v>115</v>
+      </c>
+      <c r="P52" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q52" t="s">
         <v>88</v>
       </c>
-      <c r="R52" s="1" t="s">
+      <c r="R52" t="s">
         <v>89</v>
       </c>
-      <c r="S52" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="T52" s="1" t="s">
+      <c r="S52" t="s">
+        <v>18</v>
+      </c>
+      <c r="T52" t="s">
         <v>19</v>
       </c>
       <c r="U52">
@@ -4637,27 +4635,27 @@
       <c r="Y52">
         <v>1435</v>
       </c>
-      <c r="AB52" s="1" t="s">
+      <c r="AB52" t="s">
         <v>125</v>
       </c>
-      <c r="AC52" s="1" t="s">
+      <c r="AC52" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="53" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A53" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B53" s="1" t="s">
+      <c r="A53" t="s">
+        <v>15</v>
+      </c>
+      <c r="B53" t="s">
         <v>88</v>
       </c>
-      <c r="C53" s="1" t="s">
+      <c r="C53" t="s">
         <v>90</v>
       </c>
-      <c r="D53" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E53" s="1" t="s">
+      <c r="D53" t="s">
+        <v>18</v>
+      </c>
+      <c r="E53" t="s">
         <v>19</v>
       </c>
       <c r="F53">
@@ -4675,25 +4673,25 @@
       <c r="J53">
         <v>1254</v>
       </c>
-      <c r="M53" s="1" t="s">
+      <c r="M53" t="s">
         <v>125</v>
       </c>
-      <c r="N53" s="1" t="s">
+      <c r="N53" t="s">
         <v>46</v>
       </c>
-      <c r="P53" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q53" s="1" t="s">
+      <c r="P53" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q53" t="s">
         <v>88</v>
       </c>
-      <c r="R53" s="1" t="s">
+      <c r="R53" t="s">
         <v>90</v>
       </c>
-      <c r="S53" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="T53" s="1" t="s">
+      <c r="S53" t="s">
+        <v>18</v>
+      </c>
+      <c r="T53" t="s">
         <v>19</v>
       </c>
       <c r="U53">
@@ -4711,27 +4709,27 @@
       <c r="Y53">
         <v>1485</v>
       </c>
-      <c r="AB53" s="1" t="s">
+      <c r="AB53" t="s">
         <v>125</v>
       </c>
-      <c r="AC53" s="1" t="s">
+      <c r="AC53" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="54" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A54" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B54" s="1" t="s">
+      <c r="A54" t="s">
+        <v>15</v>
+      </c>
+      <c r="B54" t="s">
         <v>88</v>
       </c>
-      <c r="C54" s="1" t="s">
+      <c r="C54" t="s">
         <v>91</v>
       </c>
-      <c r="D54" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E54" s="1" t="s">
+      <c r="D54" t="s">
+        <v>18</v>
+      </c>
+      <c r="E54" t="s">
         <v>19</v>
       </c>
       <c r="F54">
@@ -4749,25 +4747,25 @@
       <c r="J54">
         <v>1329</v>
       </c>
-      <c r="M54" s="1" t="s">
+      <c r="M54" t="s">
         <v>125</v>
       </c>
-      <c r="N54" s="1" t="s">
+      <c r="N54" t="s">
         <v>46</v>
       </c>
-      <c r="P54" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q54" s="1" t="s">
+      <c r="P54" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q54" t="s">
         <v>88</v>
       </c>
-      <c r="R54" s="1" t="s">
+      <c r="R54" t="s">
         <v>91</v>
       </c>
-      <c r="S54" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="T54" s="1" t="s">
+      <c r="S54" t="s">
+        <v>18</v>
+      </c>
+      <c r="T54" t="s">
         <v>19</v>
       </c>
       <c r="U54">
@@ -4785,27 +4783,27 @@
       <c r="Y54">
         <v>151</v>
       </c>
-      <c r="AB54" s="1" t="s">
+      <c r="AB54" t="s">
         <v>125</v>
       </c>
-      <c r="AC54" s="1" t="s">
+      <c r="AC54" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="55" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A55" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B55" s="1" t="s">
+      <c r="A55" t="s">
+        <v>15</v>
+      </c>
+      <c r="B55" t="s">
         <v>88</v>
       </c>
-      <c r="C55" s="1" t="s">
+      <c r="C55" t="s">
         <v>92</v>
       </c>
-      <c r="D55" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E55" s="1" t="s">
+      <c r="D55" t="s">
+        <v>18</v>
+      </c>
+      <c r="E55" t="s">
         <v>19</v>
       </c>
       <c r="F55">
@@ -4823,25 +4821,25 @@
       <c r="J55">
         <v>2015</v>
       </c>
-      <c r="M55" s="1" t="s">
+      <c r="M55" t="s">
         <v>126</v>
       </c>
-      <c r="N55" s="1" t="s">
+      <c r="N55" t="s">
         <v>46</v>
       </c>
-      <c r="P55" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q55" s="1" t="s">
+      <c r="P55" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q55" t="s">
         <v>88</v>
       </c>
-      <c r="R55" s="1" t="s">
+      <c r="R55" t="s">
         <v>92</v>
       </c>
-      <c r="S55" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="T55" s="1" t="s">
+      <c r="S55" t="s">
+        <v>18</v>
+      </c>
+      <c r="T55" t="s">
         <v>19</v>
       </c>
       <c r="U55">
@@ -4859,27 +4857,27 @@
       <c r="Y55">
         <v>214</v>
       </c>
-      <c r="AB55" s="1" t="s">
+      <c r="AB55" t="s">
         <v>126</v>
       </c>
-      <c r="AC55" s="1" t="s">
+      <c r="AC55" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="56" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A56" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B56" s="1" t="s">
+      <c r="A56" t="s">
+        <v>15</v>
+      </c>
+      <c r="B56" t="s">
         <v>88</v>
       </c>
-      <c r="C56" s="1" t="s">
+      <c r="C56" t="s">
         <v>93</v>
       </c>
-      <c r="D56" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E56" s="1" t="s">
+      <c r="D56" t="s">
+        <v>18</v>
+      </c>
+      <c r="E56" t="s">
         <v>19</v>
       </c>
       <c r="F56">
@@ -4897,25 +4895,25 @@
       <c r="J56">
         <v>891</v>
       </c>
-      <c r="M56" s="1" t="s">
+      <c r="M56" t="s">
         <v>127</v>
       </c>
-      <c r="N56" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="P56" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q56" s="1" t="s">
+      <c r="N56" t="s">
+        <v>115</v>
+      </c>
+      <c r="P56" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q56" t="s">
         <v>88</v>
       </c>
-      <c r="R56" s="1" t="s">
+      <c r="R56" t="s">
         <v>93</v>
       </c>
-      <c r="S56" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="T56" s="1" t="s">
+      <c r="S56" t="s">
+        <v>18</v>
+      </c>
+      <c r="T56" t="s">
         <v>19</v>
       </c>
       <c r="U56">
@@ -4933,27 +4931,27 @@
       <c r="Y56">
         <v>1108</v>
       </c>
-      <c r="AB56" s="1" t="s">
+      <c r="AB56" t="s">
         <v>127</v>
       </c>
-      <c r="AC56" s="1" t="s">
+      <c r="AC56" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="57" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A57" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B57" s="1" t="s">
+      <c r="A57" t="s">
+        <v>15</v>
+      </c>
+      <c r="B57" t="s">
         <v>88</v>
       </c>
-      <c r="C57" s="1" t="s">
+      <c r="C57" t="s">
         <v>94</v>
       </c>
-      <c r="D57" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E57" s="1" t="s">
+      <c r="D57" t="s">
+        <v>18</v>
+      </c>
+      <c r="E57" t="s">
         <v>19</v>
       </c>
       <c r="F57">
@@ -4971,25 +4969,25 @@
       <c r="J57">
         <v>1531</v>
       </c>
-      <c r="M57" s="1" t="s">
+      <c r="M57" t="s">
         <v>128</v>
       </c>
-      <c r="N57" s="1" t="s">
+      <c r="N57" t="s">
         <v>46</v>
       </c>
-      <c r="P57" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q57" s="1" t="s">
+      <c r="P57" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q57" t="s">
         <v>88</v>
       </c>
-      <c r="R57" s="1" t="s">
+      <c r="R57" t="s">
         <v>94</v>
       </c>
-      <c r="S57" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="T57" s="1" t="s">
+      <c r="S57" t="s">
+        <v>18</v>
+      </c>
+      <c r="T57" t="s">
         <v>19</v>
       </c>
       <c r="U57">
@@ -5007,27 +5005,27 @@
       <c r="Y57">
         <v>1485</v>
       </c>
-      <c r="AB57" s="1" t="s">
+      <c r="AB57" t="s">
         <v>128</v>
       </c>
-      <c r="AC57" s="1" t="s">
+      <c r="AC57" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="58" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A58" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B58" s="1" t="s">
+      <c r="A58" t="s">
+        <v>15</v>
+      </c>
+      <c r="B58" t="s">
         <v>88</v>
       </c>
-      <c r="C58" s="1" t="s">
+      <c r="C58" t="s">
         <v>95</v>
       </c>
-      <c r="D58" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E58" s="1" t="s">
+      <c r="D58" t="s">
+        <v>18</v>
+      </c>
+      <c r="E58" t="s">
         <v>19</v>
       </c>
       <c r="F58">
@@ -5045,25 +5043,25 @@
       <c r="J58">
         <v>1263</v>
       </c>
-      <c r="M58" s="1" t="s">
+      <c r="M58" t="s">
         <v>129</v>
       </c>
-      <c r="N58" s="1" t="s">
+      <c r="N58" t="s">
         <v>46</v>
       </c>
-      <c r="P58" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q58" s="1" t="s">
+      <c r="P58" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q58" t="s">
         <v>88</v>
       </c>
-      <c r="R58" s="1" t="s">
+      <c r="R58" t="s">
         <v>95</v>
       </c>
-      <c r="S58" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="T58" s="1" t="s">
+      <c r="S58" t="s">
+        <v>18</v>
+      </c>
+      <c r="T58" t="s">
         <v>19</v>
       </c>
       <c r="U58">
@@ -5081,27 +5079,27 @@
       <c r="Y58">
         <v>1379</v>
       </c>
-      <c r="AB58" s="1" t="s">
+      <c r="AB58" t="s">
         <v>129</v>
       </c>
-      <c r="AC58" s="1" t="s">
+      <c r="AC58" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="59" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A59" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B59" s="1" t="s">
+      <c r="A59" t="s">
+        <v>15</v>
+      </c>
+      <c r="B59" t="s">
         <v>88</v>
       </c>
-      <c r="C59" s="1" t="s">
+      <c r="C59" t="s">
         <v>96</v>
       </c>
-      <c r="D59" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E59" s="1" t="s">
+      <c r="D59" t="s">
+        <v>18</v>
+      </c>
+      <c r="E59" t="s">
         <v>19</v>
       </c>
       <c r="F59">
@@ -5119,25 +5117,25 @@
       <c r="J59">
         <v>257</v>
       </c>
-      <c r="M59" s="1" t="s">
+      <c r="M59" t="s">
         <v>130</v>
       </c>
-      <c r="N59" s="1" t="s">
+      <c r="N59" t="s">
         <v>46</v>
       </c>
-      <c r="P59" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q59" s="1" t="s">
+      <c r="P59" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q59" t="s">
         <v>88</v>
       </c>
-      <c r="R59" s="1" t="s">
+      <c r="R59" t="s">
         <v>96</v>
       </c>
-      <c r="S59" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="T59" s="1" t="s">
+      <c r="S59" t="s">
+        <v>18</v>
+      </c>
+      <c r="T59" t="s">
         <v>19</v>
       </c>
       <c r="U59">
@@ -5155,27 +5153,27 @@
       <c r="Y59">
         <v>2965</v>
       </c>
-      <c r="AB59" s="1" t="s">
+      <c r="AB59" t="s">
         <v>130</v>
       </c>
-      <c r="AC59" s="1" t="s">
+      <c r="AC59" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="60" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A60" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B60" s="1" t="s">
+      <c r="A60" t="s">
+        <v>15</v>
+      </c>
+      <c r="B60" t="s">
         <v>88</v>
       </c>
-      <c r="C60" s="1" t="s">
+      <c r="C60" t="s">
         <v>97</v>
       </c>
-      <c r="D60" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E60" s="1" t="s">
+      <c r="D60" t="s">
+        <v>18</v>
+      </c>
+      <c r="E60" t="s">
         <v>19</v>
       </c>
       <c r="F60">
@@ -5193,25 +5191,25 @@
       <c r="J60">
         <v>867</v>
       </c>
-      <c r="M60" s="1" t="s">
+      <c r="M60" t="s">
         <v>131</v>
       </c>
-      <c r="N60" s="1" t="s">
+      <c r="N60" t="s">
         <v>32</v>
       </c>
-      <c r="P60" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q60" s="1" t="s">
+      <c r="P60" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q60" t="s">
         <v>88</v>
       </c>
-      <c r="R60" s="1" t="s">
+      <c r="R60" t="s">
         <v>97</v>
       </c>
-      <c r="S60" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="T60" s="1" t="s">
+      <c r="S60" t="s">
+        <v>18</v>
+      </c>
+      <c r="T60" t="s">
         <v>19</v>
       </c>
       <c r="U60">
@@ -5229,27 +5227,27 @@
       <c r="Y60">
         <v>107</v>
       </c>
-      <c r="AB60" s="1" t="s">
+      <c r="AB60" t="s">
         <v>131</v>
       </c>
-      <c r="AC60" s="1" t="s">
+      <c r="AC60" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="61" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A61" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B61" s="1" t="s">
+      <c r="A61" t="s">
+        <v>15</v>
+      </c>
+      <c r="B61" t="s">
         <v>88</v>
       </c>
-      <c r="C61" s="1" t="s">
+      <c r="C61" t="s">
         <v>98</v>
       </c>
-      <c r="D61" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E61" s="1" t="s">
+      <c r="D61" t="s">
+        <v>18</v>
+      </c>
+      <c r="E61" t="s">
         <v>19</v>
       </c>
       <c r="F61">
@@ -5267,25 +5265,25 @@
       <c r="J61">
         <v>175</v>
       </c>
-      <c r="M61" s="1" t="s">
+      <c r="M61" t="s">
         <v>132</v>
       </c>
-      <c r="N61" s="1" t="s">
+      <c r="N61" t="s">
         <v>46</v>
       </c>
-      <c r="P61" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q61" s="1" t="s">
+      <c r="P61" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q61" t="s">
         <v>88</v>
       </c>
-      <c r="R61" s="1" t="s">
+      <c r="R61" t="s">
         <v>98</v>
       </c>
-      <c r="S61" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="T61" s="1" t="s">
+      <c r="S61" t="s">
+        <v>18</v>
+      </c>
+      <c r="T61" t="s">
         <v>19</v>
       </c>
       <c r="U61">
@@ -5303,27 +5301,27 @@
       <c r="Y61">
         <v>1541</v>
       </c>
-      <c r="AB61" s="1" t="s">
+      <c r="AB61" t="s">
         <v>132</v>
       </c>
-      <c r="AC61" s="1" t="s">
+      <c r="AC61" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="62" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A62" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B62" s="1" t="s">
+      <c r="A62" t="s">
+        <v>15</v>
+      </c>
+      <c r="B62" t="s">
         <v>88</v>
       </c>
-      <c r="C62" s="1" t="s">
+      <c r="C62" t="s">
         <v>99</v>
       </c>
-      <c r="D62" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E62" s="1" t="s">
+      <c r="D62" t="s">
+        <v>18</v>
+      </c>
+      <c r="E62" t="s">
         <v>19</v>
       </c>
       <c r="F62">
@@ -5341,25 +5339,25 @@
       <c r="J62">
         <v>1311</v>
       </c>
-      <c r="M62" s="1" t="s">
+      <c r="M62" t="s">
         <v>133</v>
       </c>
-      <c r="N62" s="1" t="s">
+      <c r="N62" t="s">
         <v>46</v>
       </c>
-      <c r="P62" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q62" s="1" t="s">
+      <c r="P62" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q62" t="s">
         <v>88</v>
       </c>
-      <c r="R62" s="1" t="s">
+      <c r="R62" t="s">
         <v>99</v>
       </c>
-      <c r="S62" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="T62" s="1" t="s">
+      <c r="S62" t="s">
+        <v>18</v>
+      </c>
+      <c r="T62" t="s">
         <v>19</v>
       </c>
       <c r="U62">
@@ -5377,27 +5375,27 @@
       <c r="Y62">
         <v>149</v>
       </c>
-      <c r="AB62" s="1" t="s">
+      <c r="AB62" t="s">
         <v>133</v>
       </c>
-      <c r="AC62" s="1" t="s">
+      <c r="AC62" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="63" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A63" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B63" s="1" t="s">
+      <c r="A63" t="s">
+        <v>15</v>
+      </c>
+      <c r="B63" t="s">
         <v>100</v>
       </c>
-      <c r="C63" s="1" t="s">
+      <c r="C63" t="s">
         <v>101</v>
       </c>
-      <c r="D63" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E63" s="1" t="s">
+      <c r="D63" t="s">
+        <v>18</v>
+      </c>
+      <c r="E63" t="s">
         <v>19</v>
       </c>
       <c r="F63">
@@ -5415,25 +5413,25 @@
       <c r="J63">
         <v>133</v>
       </c>
-      <c r="M63" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="N63" s="1" t="s">
+      <c r="M63" t="s">
+        <v>115</v>
+      </c>
+      <c r="N63" t="s">
         <v>46</v>
       </c>
-      <c r="P63" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q63" s="1" t="s">
+      <c r="P63" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q63" t="s">
         <v>100</v>
       </c>
-      <c r="R63" s="1" t="s">
+      <c r="R63" t="s">
         <v>101</v>
       </c>
-      <c r="S63" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="T63" s="1" t="s">
+      <c r="S63" t="s">
+        <v>18</v>
+      </c>
+      <c r="T63" t="s">
         <v>19</v>
       </c>
       <c r="U63">
@@ -5451,27 +5449,27 @@
       <c r="Y63">
         <v>1309</v>
       </c>
-      <c r="AB63" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="AC63" s="1" t="s">
+      <c r="AB63" t="s">
+        <v>115</v>
+      </c>
+      <c r="AC63" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="64" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A64" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B64" s="1" t="s">
+      <c r="A64" t="s">
+        <v>15</v>
+      </c>
+      <c r="B64" t="s">
         <v>100</v>
       </c>
-      <c r="C64" s="1" t="s">
+      <c r="C64" t="s">
         <v>102</v>
       </c>
-      <c r="D64" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E64" s="1" t="s">
+      <c r="D64" t="s">
+        <v>18</v>
+      </c>
+      <c r="E64" t="s">
         <v>19</v>
       </c>
       <c r="F64">
@@ -5489,25 +5487,25 @@
       <c r="J64">
         <v>981</v>
       </c>
-      <c r="M64" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="N64" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="P64" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q64" s="1" t="s">
+      <c r="M64" t="s">
+        <v>115</v>
+      </c>
+      <c r="N64" t="s">
+        <v>115</v>
+      </c>
+      <c r="P64" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q64" t="s">
         <v>100</v>
       </c>
-      <c r="R64" s="1" t="s">
+      <c r="R64" t="s">
         <v>102</v>
       </c>
-      <c r="S64" s="1" t="s">
+      <c r="S64" t="s">
         <v>34</v>
       </c>
-      <c r="T64" s="1" t="s">
+      <c r="T64" t="s">
         <v>35</v>
       </c>
       <c r="U64">
@@ -5525,27 +5523,27 @@
       <c r="Y64">
         <v>1186</v>
       </c>
-      <c r="AB64" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="AC64" s="1" t="s">
+      <c r="AB64" t="s">
+        <v>115</v>
+      </c>
+      <c r="AC64" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="65" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A65" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B65" s="1" t="s">
+      <c r="A65" t="s">
+        <v>15</v>
+      </c>
+      <c r="B65" t="s">
         <v>100</v>
       </c>
-      <c r="C65" s="1" t="s">
+      <c r="C65" t="s">
         <v>103</v>
       </c>
-      <c r="D65" s="1" t="s">
+      <c r="D65" t="s">
         <v>104</v>
       </c>
-      <c r="E65" s="1" t="s">
+      <c r="E65" t="s">
         <v>105</v>
       </c>
       <c r="F65">
@@ -5563,25 +5561,25 @@
       <c r="J65">
         <v>2332</v>
       </c>
-      <c r="M65" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="N65" s="1" t="s">
+      <c r="M65" t="s">
+        <v>115</v>
+      </c>
+      <c r="N65" t="s">
         <v>2</v>
       </c>
-      <c r="P65" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q65" s="1" t="s">
+      <c r="P65" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q65" t="s">
         <v>100</v>
       </c>
-      <c r="R65" s="1" t="s">
+      <c r="R65" t="s">
         <v>103</v>
       </c>
-      <c r="S65" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="T65" s="1" t="s">
+      <c r="S65" t="s">
+        <v>18</v>
+      </c>
+      <c r="T65" t="s">
         <v>19</v>
       </c>
       <c r="U65">
@@ -5599,27 +5597,27 @@
       <c r="Y65">
         <v>2033</v>
       </c>
-      <c r="AB65" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="AC65" s="1" t="s">
+      <c r="AB65" t="s">
+        <v>115</v>
+      </c>
+      <c r="AC65" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="66" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A66" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B66" s="1" t="s">
+      <c r="A66" t="s">
+        <v>15</v>
+      </c>
+      <c r="B66" t="s">
         <v>100</v>
       </c>
-      <c r="C66" s="1" t="s">
+      <c r="C66" t="s">
         <v>106</v>
       </c>
-      <c r="D66" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E66" s="1" t="s">
+      <c r="D66" t="s">
+        <v>18</v>
+      </c>
+      <c r="E66" t="s">
         <v>19</v>
       </c>
       <c r="F66">
@@ -5637,25 +5635,25 @@
       <c r="J66">
         <v>86</v>
       </c>
-      <c r="M66" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="N66" s="1" t="s">
+      <c r="M66" t="s">
+        <v>115</v>
+      </c>
+      <c r="N66" t="s">
         <v>32</v>
       </c>
-      <c r="P66" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q66" s="1" t="s">
+      <c r="P66" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q66" t="s">
         <v>100</v>
       </c>
-      <c r="R66" s="1" t="s">
+      <c r="R66" t="s">
         <v>106</v>
       </c>
-      <c r="S66" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="T66" s="1" t="s">
+      <c r="S66" t="s">
+        <v>18</v>
+      </c>
+      <c r="T66" t="s">
         <v>19</v>
       </c>
       <c r="U66">
@@ -5673,27 +5671,27 @@
       <c r="Y66">
         <v>1217</v>
       </c>
-      <c r="AB66" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="AC66" s="1" t="s">
+      <c r="AB66" t="s">
+        <v>115</v>
+      </c>
+      <c r="AC66" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="67" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A67" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B67" s="1" t="s">
+      <c r="A67" t="s">
+        <v>15</v>
+      </c>
+      <c r="B67" t="s">
         <v>100</v>
       </c>
-      <c r="C67" s="1" t="s">
+      <c r="C67" t="s">
         <v>107</v>
       </c>
-      <c r="D67" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E67" s="1" t="s">
+      <c r="D67" t="s">
+        <v>18</v>
+      </c>
+      <c r="E67" t="s">
         <v>19</v>
       </c>
       <c r="F67">
@@ -5717,25 +5715,25 @@
       <c r="L67">
         <v>192</v>
       </c>
-      <c r="M67" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="N67" s="1" t="s">
+      <c r="M67" t="s">
+        <v>115</v>
+      </c>
+      <c r="N67" t="s">
         <v>46</v>
       </c>
-      <c r="P67" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q67" s="1" t="s">
+      <c r="P67" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q67" t="s">
         <v>100</v>
       </c>
-      <c r="R67" s="1" t="s">
+      <c r="R67" t="s">
         <v>107</v>
       </c>
-      <c r="S67" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="T67" s="1" t="s">
+      <c r="S67" t="s">
+        <v>18</v>
+      </c>
+      <c r="T67" t="s">
         <v>19</v>
       </c>
       <c r="U67">
@@ -5759,27 +5757,27 @@
       <c r="AA67">
         <v>188</v>
       </c>
-      <c r="AB67" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="AC67" s="1" t="s">
+      <c r="AB67" t="s">
+        <v>115</v>
+      </c>
+      <c r="AC67" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="68" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A68" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B68" s="1" t="s">
+      <c r="A68" t="s">
+        <v>15</v>
+      </c>
+      <c r="B68" t="s">
         <v>100</v>
       </c>
-      <c r="C68" s="1" t="s">
+      <c r="C68" t="s">
         <v>108</v>
       </c>
-      <c r="D68" s="1" t="s">
+      <c r="D68" t="s">
         <v>34</v>
       </c>
-      <c r="E68" s="1" t="s">
+      <c r="E68" t="s">
         <v>35</v>
       </c>
       <c r="F68">
@@ -5803,25 +5801,25 @@
       <c r="L68">
         <v>198</v>
       </c>
-      <c r="M68" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="N68" s="1" t="s">
+      <c r="M68" t="s">
+        <v>115</v>
+      </c>
+      <c r="N68" t="s">
         <v>26</v>
       </c>
-      <c r="P68" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q68" s="1" t="s">
+      <c r="P68" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q68" t="s">
         <v>100</v>
       </c>
-      <c r="R68" s="1" t="s">
+      <c r="R68" t="s">
         <v>108</v>
       </c>
-      <c r="S68" s="1" t="s">
+      <c r="S68" t="s">
         <v>118</v>
       </c>
-      <c r="T68" s="1" t="s">
+      <c r="T68" t="s">
         <v>119</v>
       </c>
       <c r="U68">
@@ -5845,27 +5843,27 @@
       <c r="AA68">
         <v>211</v>
       </c>
-      <c r="AB68" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="AC68" s="1" t="s">
+      <c r="AB68" t="s">
+        <v>115</v>
+      </c>
+      <c r="AC68" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="69" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A69" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B69" s="1" t="s">
+      <c r="A69" t="s">
+        <v>15</v>
+      </c>
+      <c r="B69" t="s">
         <v>100</v>
       </c>
-      <c r="C69" s="1" t="s">
+      <c r="C69" t="s">
         <v>109</v>
       </c>
-      <c r="D69" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E69" s="1" t="s">
+      <c r="D69" t="s">
+        <v>18</v>
+      </c>
+      <c r="E69" t="s">
         <v>19</v>
       </c>
       <c r="F69">
@@ -5889,25 +5887,25 @@
       <c r="L69">
         <v>219</v>
       </c>
-      <c r="M69" s="1" t="s">
+      <c r="M69" t="s">
         <v>125</v>
       </c>
-      <c r="N69" s="1" t="s">
+      <c r="N69" t="s">
         <v>46</v>
       </c>
-      <c r="P69" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q69" s="1" t="s">
+      <c r="P69" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q69" t="s">
         <v>100</v>
       </c>
-      <c r="R69" s="1" t="s">
+      <c r="R69" t="s">
         <v>109</v>
       </c>
-      <c r="S69" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="T69" s="1" t="s">
+      <c r="S69" t="s">
+        <v>18</v>
+      </c>
+      <c r="T69" t="s">
         <v>19</v>
       </c>
       <c r="U69">
@@ -5931,27 +5929,27 @@
       <c r="AA69">
         <v>198</v>
       </c>
-      <c r="AB69" s="1" t="s">
+      <c r="AB69" t="s">
         <v>125</v>
       </c>
-      <c r="AC69" s="1" t="s">
+      <c r="AC69" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="70" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A70" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B70" s="1" t="s">
+      <c r="A70" t="s">
+        <v>15</v>
+      </c>
+      <c r="B70" t="s">
         <v>100</v>
       </c>
-      <c r="C70" s="1" t="s">
+      <c r="C70" t="s">
         <v>110</v>
       </c>
-      <c r="D70" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E70" s="1" t="s">
+      <c r="D70" t="s">
+        <v>18</v>
+      </c>
+      <c r="E70" t="s">
         <v>19</v>
       </c>
       <c r="F70">
@@ -5975,25 +5973,25 @@
       <c r="L70">
         <v>252</v>
       </c>
-      <c r="M70" s="1" t="s">
+      <c r="M70" t="s">
         <v>131</v>
       </c>
-      <c r="N70" s="1" t="s">
+      <c r="N70" t="s">
         <v>32</v>
       </c>
-      <c r="P70" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q70" s="1" t="s">
+      <c r="P70" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q70" t="s">
         <v>100</v>
       </c>
-      <c r="R70" s="1" t="s">
+      <c r="R70" t="s">
         <v>110</v>
       </c>
-      <c r="S70" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="T70" s="1" t="s">
+      <c r="S70" t="s">
+        <v>18</v>
+      </c>
+      <c r="T70" t="s">
         <v>19</v>
       </c>
       <c r="U70">
@@ -6017,18 +6015,763 @@
       <c r="AA70">
         <v>253</v>
       </c>
-      <c r="AB70" s="1" t="s">
+      <c r="AB70" t="s">
         <v>131</v>
       </c>
-      <c r="AC70" s="1" t="s">
+      <c r="AC70" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="76" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A76" s="4"/>
+      <c r="A76" s="1"/>
+      <c r="G76">
+        <f>G3/1000</f>
+        <v>0.19800000000000001</v>
+      </c>
+    </row>
+    <row r="77" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="G77">
+        <f t="shared" ref="G77:G140" si="0">G4/1000</f>
+        <v>0.19400000000000001</v>
+      </c>
+    </row>
+    <row r="78" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="G78">
+        <f t="shared" si="0"/>
+        <v>0.21299999999999999</v>
+      </c>
     </row>
     <row r="79" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="C79" s="5"/>
+      <c r="G79">
+        <f t="shared" si="0"/>
+        <v>0.20300000000000001</v>
+      </c>
+    </row>
+    <row r="80" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="G80">
+        <f t="shared" si="0"/>
+        <v>0.21099999999999999</v>
+      </c>
+    </row>
+    <row r="81" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G81">
+        <f t="shared" si="0"/>
+        <v>0.20799999999999999</v>
+      </c>
+    </row>
+    <row r="82" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G82">
+        <f t="shared" si="0"/>
+        <v>0.17299999999999999</v>
+      </c>
+    </row>
+    <row r="83" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G83">
+        <f t="shared" si="0"/>
+        <v>0.216</v>
+      </c>
+    </row>
+    <row r="84" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G84">
+        <f t="shared" si="0"/>
+        <v>0.28799999999999998</v>
+      </c>
+    </row>
+    <row r="85" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G85">
+        <f t="shared" si="0"/>
+        <v>3.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="86" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G86">
+        <f t="shared" si="0"/>
+        <v>3.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="87" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G87">
+        <f t="shared" si="0"/>
+        <v>0.17199999999999999</v>
+      </c>
+    </row>
+    <row r="88" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G88">
+        <f t="shared" si="0"/>
+        <v>0.17299999999999999</v>
+      </c>
+    </row>
+    <row r="89" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G89">
+        <f t="shared" si="0"/>
+        <v>0.17499999999999999</v>
+      </c>
+    </row>
+    <row r="90" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G90">
+        <f t="shared" si="0"/>
+        <v>0.183</v>
+      </c>
+    </row>
+    <row r="91" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G91">
+        <f t="shared" si="0"/>
+        <v>0.14199999999999999</v>
+      </c>
+    </row>
+    <row r="92" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G92">
+        <f t="shared" si="0"/>
+        <v>0.28799999999999998</v>
+      </c>
+    </row>
+    <row r="93" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G93">
+        <f t="shared" si="0"/>
+        <v>1.7000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="94" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G94">
+        <f t="shared" si="0"/>
+        <v>0.30199999999999999</v>
+      </c>
+    </row>
+    <row r="95" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G95">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G96">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G97">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G98">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G99">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G100">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G101">
+        <f t="shared" si="0"/>
+        <v>0.14199999999999999</v>
+      </c>
+    </row>
+    <row r="102" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G102">
+        <f t="shared" si="0"/>
+        <v>0.13100000000000001</v>
+      </c>
+    </row>
+    <row r="103" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G103">
+        <f t="shared" si="0"/>
+        <v>0.17299999999999999</v>
+      </c>
+    </row>
+    <row r="104" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G104">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G105">
+        <f t="shared" si="0"/>
+        <v>0.17699999999999999</v>
+      </c>
+    </row>
+    <row r="106" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G106">
+        <f t="shared" si="0"/>
+        <v>0.17599999999999999</v>
+      </c>
+    </row>
+    <row r="107" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G107">
+        <f t="shared" si="0"/>
+        <v>0.13800000000000001</v>
+      </c>
+    </row>
+    <row r="108" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G108">
+        <f t="shared" si="0"/>
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="109" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G109">
+        <f t="shared" si="0"/>
+        <v>0.108</v>
+      </c>
+    </row>
+    <row r="110" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G110">
+        <f t="shared" si="0"/>
+        <v>2.3E-2</v>
+      </c>
+    </row>
+    <row r="111" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G111">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G112">
+        <f t="shared" si="0"/>
+        <v>0.26700000000000002</v>
+      </c>
+    </row>
+    <row r="113" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G113">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G114">
+        <f t="shared" si="0"/>
+        <v>0.30199999999999999</v>
+      </c>
+    </row>
+    <row r="115" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G115">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G116">
+        <f t="shared" si="0"/>
+        <v>0.41799999999999998</v>
+      </c>
+    </row>
+    <row r="117" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G117">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G118">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G119">
+        <f t="shared" si="0"/>
+        <v>0.19900000000000001</v>
+      </c>
+    </row>
+    <row r="120" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G120">
+        <f t="shared" si="0"/>
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="121" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G121">
+        <f t="shared" si="0"/>
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="122" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G122">
+        <f t="shared" si="0"/>
+        <v>0.17799999999999999</v>
+      </c>
+    </row>
+    <row r="123" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G123">
+        <f t="shared" si="0"/>
+        <v>0.17100000000000001</v>
+      </c>
+    </row>
+    <row r="124" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G124">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G125">
+        <f t="shared" si="0"/>
+        <v>0.193</v>
+      </c>
+    </row>
+    <row r="126" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G126">
+        <f t="shared" si="0"/>
+        <v>1.9E-2</v>
+      </c>
+    </row>
+    <row r="127" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G127">
+        <f t="shared" si="0"/>
+        <v>0.185</v>
+      </c>
+    </row>
+    <row r="128" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G128">
+        <f t="shared" si="0"/>
+        <v>0.17599999999999999</v>
+      </c>
+    </row>
+    <row r="129" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G129">
+        <f t="shared" si="0"/>
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="130" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G130">
+        <f t="shared" si="0"/>
+        <v>0.188</v>
+      </c>
+    </row>
+    <row r="131" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G131">
+        <f t="shared" si="0"/>
+        <v>0.20699999999999999</v>
+      </c>
+    </row>
+    <row r="132" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G132">
+        <f t="shared" si="0"/>
+        <v>0.16700000000000001</v>
+      </c>
+    </row>
+    <row r="133" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G133">
+        <f t="shared" si="0"/>
+        <v>0.223</v>
+      </c>
+    </row>
+    <row r="134" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G134">
+        <f t="shared" si="0"/>
+        <v>0.186</v>
+      </c>
+    </row>
+    <row r="135" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G135">
+        <f t="shared" si="0"/>
+        <v>2.1000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="136" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G136">
+        <f t="shared" si="0"/>
+        <v>0.154</v>
+      </c>
+    </row>
+    <row r="137" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G137">
+        <f t="shared" si="0"/>
+        <v>0.216</v>
+      </c>
+    </row>
+    <row r="138" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G138">
+        <f t="shared" si="0"/>
+        <v>0.17799999999999999</v>
+      </c>
+    </row>
+    <row r="139" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G139">
+        <f t="shared" si="0"/>
+        <v>0.26900000000000002</v>
+      </c>
+    </row>
+    <row r="140" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G140">
+        <f t="shared" si="0"/>
+        <v>0.182</v>
+      </c>
+    </row>
+    <row r="141" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G141">
+        <f t="shared" ref="G141:G189" si="1">G68/1000</f>
+        <v>0.193</v>
+      </c>
+    </row>
+    <row r="142" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G142">
+        <f t="shared" si="1"/>
+        <v>0.188</v>
+      </c>
+    </row>
+    <row r="143" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G143">
+        <f t="shared" si="1"/>
+        <v>2.1999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="144" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G144">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G145">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G146">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G147">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G148">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G149">
+        <f t="shared" si="1"/>
+        <v>1.9800000000000002E-4</v>
+      </c>
+    </row>
+    <row r="150" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G150">
+        <f t="shared" si="1"/>
+        <v>1.94E-4</v>
+      </c>
+    </row>
+    <row r="151" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G151">
+        <f t="shared" si="1"/>
+        <v>2.13E-4</v>
+      </c>
+    </row>
+    <row r="152" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G152">
+        <f t="shared" si="1"/>
+        <v>2.03E-4</v>
+      </c>
+    </row>
+    <row r="153" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G153">
+        <f t="shared" si="1"/>
+        <v>2.1100000000000001E-4</v>
+      </c>
+    </row>
+    <row r="154" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G154">
+        <f t="shared" si="1"/>
+        <v>2.0799999999999999E-4</v>
+      </c>
+    </row>
+    <row r="155" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G155">
+        <f t="shared" si="1"/>
+        <v>1.7299999999999998E-4</v>
+      </c>
+    </row>
+    <row r="156" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G156">
+        <f t="shared" si="1"/>
+        <v>2.1599999999999999E-4</v>
+      </c>
+    </row>
+    <row r="157" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G157">
+        <f t="shared" si="1"/>
+        <v>2.8799999999999995E-4</v>
+      </c>
+    </row>
+    <row r="158" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G158">
+        <f t="shared" si="1"/>
+        <v>3.0000000000000001E-6</v>
+      </c>
+    </row>
+    <row r="159" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G159">
+        <f t="shared" si="1"/>
+        <v>3.0000000000000001E-6</v>
+      </c>
+    </row>
+    <row r="160" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G160">
+        <f t="shared" si="1"/>
+        <v>1.7199999999999998E-4</v>
+      </c>
+    </row>
+    <row r="161" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G161">
+        <f t="shared" si="1"/>
+        <v>1.7299999999999998E-4</v>
+      </c>
+    </row>
+    <row r="162" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G162">
+        <f t="shared" si="1"/>
+        <v>1.75E-4</v>
+      </c>
+    </row>
+    <row r="163" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G163">
+        <f t="shared" si="1"/>
+        <v>1.83E-4</v>
+      </c>
+    </row>
+    <row r="164" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G164">
+        <f t="shared" si="1"/>
+        <v>1.4199999999999998E-4</v>
+      </c>
+    </row>
+    <row r="165" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G165">
+        <f t="shared" si="1"/>
+        <v>2.8799999999999995E-4</v>
+      </c>
+    </row>
+    <row r="166" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G166">
+        <f t="shared" si="1"/>
+        <v>1.7E-5</v>
+      </c>
+    </row>
+    <row r="167" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G167">
+        <f t="shared" si="1"/>
+        <v>3.0199999999999997E-4</v>
+      </c>
+    </row>
+    <row r="168" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G168">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G169">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G170">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G171">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G172">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G173">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G174">
+        <f t="shared" si="1"/>
+        <v>1.4199999999999998E-4</v>
+      </c>
+    </row>
+    <row r="175" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G175">
+        <f t="shared" si="1"/>
+        <v>1.3100000000000001E-4</v>
+      </c>
+    </row>
+    <row r="176" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G176">
+        <f t="shared" si="1"/>
+        <v>1.7299999999999998E-4</v>
+      </c>
+    </row>
+    <row r="177" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G177">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G178">
+        <f t="shared" si="1"/>
+        <v>1.7699999999999999E-4</v>
+      </c>
+    </row>
+    <row r="179" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G179">
+        <f t="shared" si="1"/>
+        <v>1.76E-4</v>
+      </c>
+    </row>
+    <row r="180" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G180">
+        <f t="shared" si="1"/>
+        <v>1.3800000000000002E-4</v>
+      </c>
+    </row>
+    <row r="181" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G181">
+        <f t="shared" si="1"/>
+        <v>1.9999999999999999E-6</v>
+      </c>
+    </row>
+    <row r="182" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G182">
+        <f t="shared" si="1"/>
+        <v>1.08E-4</v>
+      </c>
+    </row>
+    <row r="183" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G183">
+        <f t="shared" si="1"/>
+        <v>2.3E-5</v>
+      </c>
+    </row>
+    <row r="184" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G184">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G185">
+        <f t="shared" si="1"/>
+        <v>2.6700000000000004E-4</v>
+      </c>
+    </row>
+    <row r="186" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G186">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G187">
+        <f t="shared" si="1"/>
+        <v>3.0199999999999997E-4</v>
+      </c>
+    </row>
+    <row r="188" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G188">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G189">
+        <f t="shared" si="1"/>
+        <v>4.1799999999999997E-4</v>
+      </c>
+    </row>
+    <row r="190" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G190">
+        <f>G117/1000</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G191">
+        <f t="shared" ref="G191:G200" si="2">G118/1000</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G192">
+        <f t="shared" si="2"/>
+        <v>1.9900000000000001E-4</v>
+      </c>
+    </row>
+    <row r="193" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G193">
+        <f t="shared" si="2"/>
+        <v>1.9999999999999999E-6</v>
+      </c>
+    </row>
+    <row r="194" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G194">
+        <f t="shared" si="2"/>
+        <v>1.9999999999999999E-6</v>
+      </c>
+    </row>
+    <row r="195" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G195">
+        <f t="shared" si="2"/>
+        <v>1.7799999999999999E-4</v>
+      </c>
+    </row>
+    <row r="196" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G196">
+        <f t="shared" si="2"/>
+        <v>1.7100000000000001E-4</v>
+      </c>
+    </row>
+    <row r="197" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G197">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G198">
+        <f t="shared" si="2"/>
+        <v>1.93E-4</v>
+      </c>
+    </row>
+    <row r="199" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G199">
+        <f t="shared" si="2"/>
+        <v>1.9000000000000001E-5</v>
+      </c>
+    </row>
+    <row r="200" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G200">
+        <f t="shared" si="2"/>
+        <v>1.85E-4</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
